--- a/multiSchoolOutput/07_School_of_Chemistry/solution_weeks_9_10.xlsx
+++ b/multiSchoolOutput/07_School_of_Chemistry/solution_weeks_9_10.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wednesday 15:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -609,12 +609,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0254_01_1.01</t>
+          <t>0113_00_G.199</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0283_01_1.01</t>
+          <t>0112_02_2.11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Monday 11:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0201_03_3.01</t>
+          <t>0110_02_2.04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0008_01_1.306</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1098,7 +1098,7 @@
         <v>86</v>
       </c>
       <c r="F12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0008_01_1.306</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1157,7 +1157,7 @@
         <v>90</v>
       </c>
       <c r="F13" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Monday 16:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1334,7 +1334,7 @@
         <v>80</v>
       </c>
       <c r="F16" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0228_06_6.10</t>
+          <t>0201_04_4.14</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tuesday 11:00</t>
+          <t>Friday 17:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0209_02_2.01</t>
+          <t>0226_-1_LG.19</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1966,12 +1966,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0008_01_1.306</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1983,7 +1983,7 @@
         <v>84</v>
       </c>
       <c r="F27" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2025,12 +2025,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0450_03_3.42</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2042,7 +2042,7 @@
         <v>6</v>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0335_04_4.3</t>
+          <t>0422_J_J.05</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2208,12 +2208,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0226_01_1.02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tuesday 16:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0201_01_1.06</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Monday 11:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2408,7 +2408,7 @@
         <v>300</v>
       </c>
       <c r="F34" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2452,12 +2452,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0008_01_1.306</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thursday 11:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2469,7 +2469,7 @@
         <v>80</v>
       </c>
       <c r="F35" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thursday 16:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2530,7 +2530,7 @@
         <v>80</v>
       </c>
       <c r="F36" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0227_00_G.05</t>
+          <t>0335_02_2.2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0008_01_1.306</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2835,7 +2835,7 @@
         <v>80</v>
       </c>
       <c r="F41" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0210_-1_B.51</t>
+          <t>0005_01_1.01</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0335_01_1.1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3001,12 +3001,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0201_00_G.06</t>
+          <t>0201_00_G.08</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0335_04_4.3</t>
+          <t>0422_J_J.03</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3123,12 +3123,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0112_-1_B.06</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0201_01_1.06</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Thursday 11:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3201,7 +3201,7 @@
         <v>300</v>
       </c>
       <c r="F47" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -3306,12 +3306,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0335_04_4.3</t>
+          <t>0422_J_J.03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0201_01_1.06</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Thursday 16:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3384,7 +3384,7 @@
         <v>300</v>
       </c>
       <c r="F50" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0227_02_2.30</t>
+          <t>0113_01_1.26</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0201_01_1.06</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tuesday 11:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3750,7 +3750,7 @@
         <v>300</v>
       </c>
       <c r="F56" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -3794,12 +3794,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0335_04_4.3</t>
+          <t>0422_J_J.03</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0422_J_J.03</t>
+          <t>0422_J_J.05</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3916,12 +3916,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0226_-1_LG.19</t>
+          <t>0209_02_2.01</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0113_02_2.65</t>
+          <t>0209_02_2.01</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0008_01_1.306</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4116,7 +4116,7 @@
         <v>90</v>
       </c>
       <c r="F62" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0335_01_1.3</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4343,12 +4343,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0209_02_2.01</t>
+          <t>0226_-1_LG.19</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0335_04_4.3</t>
+          <t>0422_J_J.05</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0210_00_G.04</t>
+          <t>0226_00_GF.14</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Friday 15:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4543,7 +4543,7 @@
         <v>130</v>
       </c>
       <c r="F69" t="n">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -4587,12 +4587,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0110_02_2.01</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0422_J_J.03</t>
+          <t>0422_J_J.05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4770,12 +4770,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0227_03_3.13</t>
+          <t>0113_00M_00M.07</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0008_00_G.267</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0422_J_J.03</t>
+          <t>0335_04_4.3</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0422_J_J.05</t>
+          <t>0422_J_J.03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0228_-1_LG.06</t>
+          <t>0112_-1_B.01</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0227_03_3.30</t>
+          <t>0113_00M_00M.03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0335_03_3.1</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5502,12 +5502,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0113_00_G.03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0422_J_J.05</t>
+          <t>0335_04_4.3</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Monday 16:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0422_J_J.05</t>
+          <t>0335_04_4.3</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0335_02_2.1</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0422_J_J.03</t>
+          <t>0422_J_J.05</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0335_05_5.1</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0008_01_1.306</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6190,7 +6190,7 @@
         <v>80</v>
       </c>
       <c r="F96" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -6234,12 +6234,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0254_01_1.03</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6251,7 +6251,7 @@
         <v>15</v>
       </c>
       <c r="F97" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0005_01_1.01</t>
+          <t>0210_-1_B.51</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0113_00_G.03</t>
+          <t>0226_01_1.02</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0001_01_1.275</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Thursday 16:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tuesday 11:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6600,12 +6600,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0112_-1_B.01</t>
+          <t>0228_-1_LG.06</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tuesday 16:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">

--- a/multiSchoolOutput/07_School_of_Chemistry/solution_weeks_9_10.xlsx
+++ b/multiSchoolOutput/07_School_of_Chemistry/solution_weeks_9_10.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M157"/>
+  <dimension ref="A1:M153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,12 +491,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0210_00_G.04</t>
+          <t>0226_00_GF.14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Monday 11:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -508,7 +508,7 @@
         <v>130</v>
       </c>
       <c r="F2" t="n">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -555,7 +555,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -609,12 +609,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0113_00_G.199</t>
+          <t>0201_02_2.06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -626,7 +626,7 @@
         <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -668,12 +668,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0201_04_4.14A</t>
+          <t>0228_02_2.18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -685,7 +685,7 @@
         <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -727,12 +727,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0201_04_4.14A</t>
+          <t>0227_02_2.39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -744,7 +744,7 @@
         <v>11</v>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0112_02_2.11</t>
+          <t>0228_02_2.18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -845,12 +845,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0201_05_5.05</t>
+          <t>0450_01_1.50</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -862,7 +862,7 @@
         <v>51</v>
       </c>
       <c r="F8" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Monday 16:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0110_02_2.04</t>
+          <t>0335_01_1.16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0201_01_1.02</t>
+          <t>0113_01M_01M.452</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1098,7 +1098,7 @@
         <v>86</v>
       </c>
       <c r="F12" t="n">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0201_01_1.02</t>
+          <t>0113_01M_01M.452</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1157,7 +1157,7 @@
         <v>90</v>
       </c>
       <c r="F13" t="n">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0201_01_1.02</t>
+          <t>0001_00_G.159</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1334,7 +1334,7 @@
         <v>80</v>
       </c>
       <c r="F16" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0005_00_G.01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1393,7 +1393,7 @@
         <v>50</v>
       </c>
       <c r="F17" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1430,17 +1430,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E:NWVN88C56K</t>
+          <t>E:43YUFRDV6X</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0225_02_2.201</t>
+          <t>0228_11_11.06</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1449,33 +1449,33 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>400</v>
+        <v>13</v>
       </c>
       <c r="F18" t="n">
-        <v>458</v>
+        <v>18</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chemistry - Annual Health &amp; Safety Briefing</t>
+          <t>CP4P - Introduction and workshop</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Workshop</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CHEM08019_SV1_YR_2024/5, CHEM08016_SV1_SEM1_2024/5, CHPH09005_SV1_YR_2024/5, CHPH08002_SV1_YR_2024/5, CHEM09007_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5</t>
+          <t>CHPH10006_SS1_YR_2024/5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Chemistry 2, Chemistry 1A, CP3 Physical Chemistry Laboratory, Chemistry for Chemical Physics 2, Chemistry 3P Practical and Transferable Skills, Chemistry 2A</t>
+          <t>Chemical Physics 4P: Laboratory Skills</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="L18" t="n">
         <v>9</v>
@@ -1489,17 +1489,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E:43YUFRDV6X</t>
+          <t>E:TO7ZW9RFSV</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0201_04_4.14</t>
+          <t>0131_04_4.07</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1508,36 +1508,36 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="F19" t="n">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CP4P - Introduction and workshop</t>
+          <t>How to Produce a Presentation (+ Group work)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CHPH10006_SS1_YR_2024/5</t>
+          <t>CHEM11076_SS1_SB5+_2024/5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Chemical Physics 4P: Laboratory Skills</t>
+          <t>MSc Research Project and Dissertation in Chemistry</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="L19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1548,17 +1548,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E:TO7ZW9RFSV</t>
+          <t>E:GFBHK9JXZP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0209_02_2.01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Friday 17:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1567,29 +1567,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F20" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>How to Produce a Presentation (+ Group work)</t>
+          <t>MChem/MChemPhys Placement Session</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Jointly Taught Seminar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CHEM11076_SS1_SB5+_2024/5</t>
+          <t>CHEM10059_SS1_SEM1_2024/5, CHEM10060_SS1_SEM2_2024/5, CHPH10006_SS1_YR_2024/5</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>MSc Research Project and Dissertation in Chemistry</t>
+          <t>Chemistry 4P: Group Research Project (Semester 1), Chemistry 4P: Group Research Project (Semester 2), Chemical Physics 4P: Laboratory Skills</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1607,17 +1607,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E:GFBHK9JXZP</t>
+          <t>E:B5N3NGK8QV-00001</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0226_-1_LG.19</t>
+          <t>0210_00_G.04</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1626,29 +1626,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="F21" t="n">
-        <v>70</v>
+        <v>139</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>MChem/MChemPhys Placement Session</t>
+          <t>Lab Safety and COSHH Lecture</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Jointly Taught Seminar</t>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>CHEM10059_SS1_SEM1_2024/5, CHEM10060_SS1_SEM2_2024/5, CHPH10006_SS1_YR_2024/5</t>
+          <t>CHEM08016_SV1_SEM1_2024/5, CHEM08028_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Chemistry 4P: Group Research Project (Semester 1), Chemistry 4P: Group Research Project (Semester 2), Chemical Physics 4P: Laboratory Skills</t>
+          <t>Chemistry 1A, Chemistry for Chemical Engineers 1A</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1666,7 +1666,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E:B5N3NGK8QV-00001</t>
+          <t>E:B5N3NGK8QV</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Friday 15:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1725,17 +1725,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E:B5N3NGK8QV</t>
+          <t>E:OH1WX8DOZI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0210_00_G.04</t>
+          <t>0226_00_GF.14</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wednesday 15:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1744,19 +1744,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="F23" t="n">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lab Safety and COSHH Lecture</t>
+          <t>Chemistry 1A Report Writing - Workshop/Fri PM</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Workshop</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1770,7 +1770,7 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>50</v>
+        <v>170</v>
       </c>
       <c r="L23" t="n">
         <v>10</v>
@@ -1784,17 +1784,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E:OH1WX8DOZI</t>
+          <t>E:7ZIXZVGTBS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0228_-1_LG.09</t>
+          <t>0228_-1_LG.11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1803,14 +1803,14 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F24" t="n">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chemistry 1A Report Writing - Workshop/Fri PM</t>
+          <t>Chemistry 1A Report Writing - Workshop/Tue AM</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="L24" t="n">
         <v>10</v>
@@ -1843,17 +1843,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>E:7ZIXZVGTBS</t>
+          <t>E:74ELYQC3VO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0226_-1_LG.10</t>
+          <t>0001_01_1.264</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1862,14 +1862,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="F25" t="n">
-        <v>72</v>
+        <v>150</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chemistry 1A Report Writing - Workshop/Tue AM</t>
+          <t>Chemistry 1A Report Writing - Workshop/Wed PM</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1879,16 +1879,16 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>CHEM08016_SV1_SEM1_2024/5, CHEM08028_SV1_SEM1_2024/5</t>
+          <t>CHEM08028_SV1_SEM1_2024/5, CHEM08016_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Chemistry 1A, Chemistry for Chemical Engineers 1A</t>
+          <t>Chemistry for Chemical Engineers 1A, Chemistry 1A</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="L25" t="n">
         <v>10</v>
@@ -1902,17 +1902,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>E:74ELYQC3VO</t>
+          <t>E:AT6OIXYRUL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0228_-1_LG.09</t>
+          <t>0113_01M_01M.452</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wednesday 14:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1924,11 +1924,11 @@
         <v>84</v>
       </c>
       <c r="F26" t="n">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chemistry 1A Report Writing - Workshop/Wed PM</t>
+          <t>Chemistry 1A Report Writing - Workshop/Tue PM</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CHEM08028_SV1_SEM1_2024/5, CHEM08016_SV1_SEM1_2024/5</t>
+          <t>CHEM08016_SV1_SEM1_2024/5, CHEM08028_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Chemistry for Chemical Engineers 1A, Chemistry 1A</t>
+          <t>Chemistry 1A, Chemistry for Chemical Engineers 1A</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1961,17 +1961,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>E:AT6OIXYRUL</t>
+          <t>E:SM6WCKCNMR</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0201_01_1.02</t>
+          <t>0113_00M_00M.03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1980,36 +1980,38 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="F27" t="n">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chemistry 1A Report Writing - Workshop/Tue PM</t>
+          <t>Advanced Topics in Chemical Physics - lecture</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>CHEM08016_SV1_SEM1_2024/5, CHEM08028_SV1_SEM1_2024/5</t>
+          <t>CHPH11004_SS1_YR_2024/5</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Chemistry 1A, Chemistry for Chemical Engineers 1A</t>
+          <t>Advanced Topics in Chemical Physics</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>170</v>
-      </c>
-      <c r="L27" t="n">
-        <v>10</v>
+        <v>50</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 14, 15, 16, 17</t>
+        </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2020,17 +2022,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>E:SM6WCKCNMR</t>
+          <t>E:IIZUCYJ4XZ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0450_03_3.42</t>
+          <t>0201_02_2.14</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2039,14 +2041,14 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="F28" t="n">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Advanced Topics in Chemical Physics - lecture</t>
+          <t>Advanced Physical Chemistry - Lecture</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2056,12 +2058,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CHPH11004_SS1_YR_2024/5</t>
+          <t>CHEM10056_SV1_SEM1_2024/5, CHEM10056_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Advanced Topics in Chemical Physics</t>
+          <t>Advanced Physical Chemistry, Advanced Physical Chemistry</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2069,7 +2071,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>10, 11, 12, 14, 15, 16, 17</t>
+          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2081,17 +2083,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>E:IIZUCYJ4XZ</t>
+          <t>E:QLXTYG27P7</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0335_04_4.3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wednesday 16:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2100,29 +2102,29 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="F29" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Advanced Physical Chemistry - Lecture</t>
+          <t>Biological Chemistry 1A - Tutorial Group/02</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Tutorial</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>CHEM10056_SV1_SEM1_2024/5, CHEM10056_VV1_SEM1_2024/5</t>
+          <t>CHEM08022_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Advanced Physical Chemistry, Advanced Physical Chemistry</t>
+          <t>Biological Chemistry 1A</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2130,7 +2132,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
+          <t>10, 12, 14, 16, 18</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2142,17 +2144,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>E:QLXTYG27P7</t>
+          <t>E:8SRJ7SNNR7</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0422_J_J.05</t>
+          <t>0450_02_2.20</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2161,29 +2163,29 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="F30" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Biological Chemistry 1A - Tutorial Group/02</t>
+          <t>Sustainable Chemistry - Lecture</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tutorial</t>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>CHEM08022_SV1_SEM1_2024/5</t>
+          <t>CHEM10023_SV1_SEM1_2024/5, CHEM10023_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Biological Chemistry 1A</t>
+          <t>Sustainable Chemistry Level 10, Sustainable Chemistry Level 10</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2191,7 +2193,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>10, 12, 14, 16, 18</t>
+          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2203,17 +2205,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>E:8SRJ7SNNR7</t>
+          <t>E:AUZRP2C31T</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0001_00_G.159</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wednesday 14:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2222,14 +2224,14 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F31" t="n">
-        <v>50</v>
+        <v>108</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sustainable Chemistry - Lecture</t>
+          <t>Optional Courses in Chemistry PGT - Lecture</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2239,12 +2241,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>CHEM10023_SV1_SEM1_2024/5, CHEM10023_VV1_SEM1_2024/5</t>
+          <t>CHEM11081_SS1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Sustainable Chemistry Level 10, Sustainable Chemistry Level 10</t>
+          <t>Optional Courses in Chemistry PGT</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2252,7 +2254,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
+          <t>10, 11, 12, 14, 15, 16</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2264,17 +2266,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>E:AUZRP2C31T</t>
+          <t>E:KLP9U62SYM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0210_00_G.04</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Wednesday 16:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2283,14 +2285,14 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="F32" t="n">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Optional Courses in Chemistry PGT - Lecture</t>
+          <t>Chemistry 3B - Lecture</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2300,12 +2302,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>CHEM11081_SS1_SEM1_2024/5</t>
+          <t>CHEM09006_SV1_YR_2024/5, CHEM09009_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Optional Courses in Chemistry PGT</t>
+          <t>Chemistry 3B, Chemistry 3B (VS1)</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2313,7 +2315,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>10, 11, 12, 14, 15, 16</t>
+          <t>10, 11, 12, 13, 14, 16, 17, 18</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2325,17 +2327,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>E:KLP9U62SYM</t>
+          <t>E:OM3A3FTRKS-00002</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0210_00_G.04</t>
+          <t>0113_01_1.425</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Thursday 16:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2344,14 +2346,14 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>130</v>
+        <v>300</v>
       </c>
       <c r="F33" t="n">
-        <v>139</v>
+        <v>260</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chemistry 3B - Lecture</t>
+          <t>Chemistry 1A - Lecture</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2361,12 +2363,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>CHEM09006_SV1_YR_2024/5, CHEM09009_VV1_SEM1_2024/5</t>
+          <t>CHEM08016_SV1_SEM1_2024/5, CHEM08028_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Chemistry 3B, Chemistry 3B (VS1)</t>
+          <t>Chemistry 1A, Chemistry for Chemical Engineers 1A</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2374,7 +2376,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>10, 11, 12, 13, 14, 16, 17, 18</t>
+          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2386,17 +2388,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>E:OM3A3FTRKS-00002</t>
+          <t>E:NJJ4U3A55K</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0201_01_1.08</t>
+          <t>0113_01M_01M.452</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2405,14 +2407,14 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="F34" t="n">
-        <v>307</v>
+        <v>114</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chemistry 1A - Lecture</t>
+          <t>Optional Courses in Chemistry PGT - Lecture</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2422,12 +2424,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>CHEM08016_SV1_SEM1_2024/5, CHEM08028_SV1_SEM1_2024/5</t>
+          <t>CHEM11081_SS1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Chemistry 1A, Chemistry for Chemical Engineers 1A</t>
+          <t>Optional Courses in Chemistry PGT</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2435,7 +2437,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
+          <t>10, 11, 12, 14, 15, 16</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2447,17 +2449,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>E:NJJ4U3A55K</t>
+          <t>E:JC3XJJZGH2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0008_01_1.306</t>
+          <t>0113_01M_01M.452</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2469,7 +2471,7 @@
         <v>80</v>
       </c>
       <c r="F35" t="n">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2508,17 +2510,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>E:JC3XJJZGH2</t>
+          <t>E:NRCITO9WKV</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0201_01_1.02</t>
+          <t>0131_04_4.07</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2530,7 +2532,7 @@
         <v>80</v>
       </c>
       <c r="F36" t="n">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2569,17 +2571,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>E:NRCITO9WKV</t>
+          <t>E:ZDNHAP7CUP</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0008_01_1.306</t>
+          <t>0226_01_1.12</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2588,37 +2590,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="F37" t="n">
-        <v>93</v>
+        <v>44</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Optional Courses in Chemistry PGT - Lecture</t>
+          <t>Chemistry 3A - Workshop/Group B and Group E</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Workshop</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>CHEM11081_SS1_SEM1_2024/5</t>
+          <t>CHEM09005_SV1_YR_2024/5, CHEM09008_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Optional Courses in Chemistry PGT</t>
+          <t>Chemistry 3A, Chemistry 3A (VS1)</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>10, 11, 12, 14, 15, 16</t>
+          <t>10, 11, 12, 13</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2630,17 +2632,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>E:ZDNHAP7CUP</t>
+          <t>E:6UHQL2FU36</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0335_02_2.2</t>
+          <t>0001_01_1.264</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2649,37 +2651,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>44</v>
+        <v>150</v>
       </c>
       <c r="F38" t="n">
-        <v>44</v>
+        <v>150</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chemistry 3A - Workshop/Group B and Group E</t>
+          <t>Chemistry 2 - Lecture</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>CHEM09005_SV1_YR_2024/5, CHEM09008_VV1_SEM1_2024/5</t>
+          <t>CHEM08019_SV1_YR_2024/5, CHPH08002_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Chemistry 3A, Chemistry 3A (VS1)</t>
+          <t>Chemistry 2, Chemistry for Chemical Physics 2, Chemistry 2A</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>10, 11, 12, 13</t>
+          <t>9, 10, 11, 12, 13, 16, 17</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2691,17 +2693,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>E:6UHQL2FU36</t>
+          <t>E:QE8CCJSLOK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0001_01_1.264</t>
+          <t>0422_J_J.03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2710,37 +2712,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="F39" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chemistry 2 - Lecture</t>
+          <t>Chemistry 1A - Tutorial Group/05</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Tutorial</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>CHEM08019_SV1_YR_2024/5, CHPH08002_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5</t>
+          <t>CHEM08028_SV1_SEM1_2024/5, CHEM08016_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Chemistry 2, Chemistry for Chemical Physics 2, Chemistry 2A</t>
+          <t>Chemistry for Chemical Engineers 1A, Chemistry 1A</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 16, 17</t>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2752,17 +2754,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>E:QE8CCJSLOK</t>
+          <t>E:8QIN1QS54W</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0335_04_4.3</t>
+          <t>0131_04_4.07</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2771,37 +2773,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F40" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chemistry 1A - Tutorial Group/05</t>
+          <t>Optional Courses in Chemistry PGT - Lecture</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Tutorial</t>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>CHEM08028_SV1_SEM1_2024/5, CHEM08016_SV1_SEM1_2024/5</t>
+          <t>CHEM11081_SS1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Chemistry for Chemical Engineers 1A, Chemistry 1A</t>
+          <t>Optional Courses in Chemistry PGT</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19</t>
+          <t>10, 11, 12, 14, 15, 16</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2813,17 +2815,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>E:8QIN1QS54W</t>
+          <t>E:BFG3NOFM1X</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0201_01_1.02</t>
+          <t>0210_-1_B.51</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2832,14 +2834,14 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="F41" t="n">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Optional Courses in Chemistry PGT - Lecture</t>
+          <t>Advanced Organic Chemistry - Lecture</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2849,12 +2851,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>CHEM11081_SS1_SEM1_2024/5</t>
+          <t>CHEM10057_SV1_SEM1_2024/5, CHEM10057_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Optional Courses in Chemistry PGT</t>
+          <t>Advanced Organic Chemistry, Advanced Organic Chemistry</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2862,7 +2864,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>10, 11, 12, 14, 15, 16</t>
+          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2874,17 +2876,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>E:BFG3NOFM1X</t>
+          <t>E:55XTM25D2T-00001</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0005_01_1.01</t>
+          <t>0112_-1_B.06</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2893,14 +2895,14 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="F42" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Advanced Organic Chemistry - Lecture</t>
+          <t>Concepts in Medicinal and Biological Chemistry PGT - Lecture</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2910,12 +2912,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>CHEM10057_SV1_SEM1_2024/5, CHEM10057_VV1_SEM1_2024/5</t>
+          <t>CHEM10073_SS1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Advanced Organic Chemistry, Advanced Organic Chemistry</t>
+          <t>Concepts in Medicinal and Biological Chemistry PGT</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2923,7 +2925,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
+          <t>9, 10, 13, 14, 17, 18</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2935,17 +2937,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>E:55XTM25D2T-00001</t>
+          <t>E:QGSC7NW2UU-00002</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0201_00_G.06</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2954,14 +2956,14 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>25</v>
+        <v>180</v>
       </c>
       <c r="F43" t="n">
-        <v>25</v>
+        <v>193</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Concepts in Medicinal and Biological Chemistry PGT - Lecture</t>
+          <t>Biological Chemistry 2 - Lecture</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2971,12 +2973,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>CHEM10073_SS1_SEM1_2024/5</t>
+          <t>CHEM08030_SV1_SEM1_2024/5, CHEM08030_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Concepts in Medicinal and Biological Chemistry PGT</t>
+          <t>Biological Chemistry 2, Biological Chemistry 2</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -2984,7 +2986,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>9, 10, 13, 14, 17, 18</t>
+          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -2996,17 +2998,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>E:QGSC7NW2UU-00002</t>
+          <t>E:6Q3RILUI6J</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0201_00_G.08</t>
+          <t>0335_04_4.3</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3015,29 +3017,29 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>180</v>
+        <v>59</v>
       </c>
       <c r="F44" t="n">
-        <v>193</v>
+        <v>60</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Biological Chemistry 2 - Lecture</t>
+          <t>Biological Chemistry 1A - Tutorial Group/07</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Tutorial</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>CHEM08030_SV1_SEM1_2024/5, CHEM08030_VV1_SEM1_2024/5</t>
+          <t>CHEM08022_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Biological Chemistry 2, Biological Chemistry 2</t>
+          <t>Biological Chemistry 1A</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -3045,7 +3047,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
+          <t>10, 12, 14, 16, 18</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3057,17 +3059,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>E:6Q3RILUI6J</t>
+          <t>E:FIUB7K3QGY</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0422_J_J.03</t>
+          <t>0335_01_1.1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3076,29 +3078,29 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="F45" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Biological Chemistry 1A - Tutorial Group/07</t>
+          <t>Concepts in Analytical Chemistry PGT - Lecture</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Tutorial</t>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>CHEM08022_SV1_SEM1_2024/5</t>
+          <t>CHEM10075_SS1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Biological Chemistry 1A</t>
+          <t>Concepts in Analytical Chemistry PGT</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3106,7 +3108,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>10, 12, 14, 16, 18</t>
+          <t>9, 10, 14, 15, 16, 17, 18</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3118,17 +3120,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>E:FIUB7K3QGY</t>
+          <t>E:OM3A3FTRKS-00003</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0113_01_1.425</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3137,14 +3139,14 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>25</v>
+        <v>300</v>
       </c>
       <c r="F46" t="n">
-        <v>25</v>
+        <v>260</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Concepts in Analytical Chemistry PGT - Lecture</t>
+          <t>Chemistry 1A - Lecture</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3154,12 +3156,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>CHEM10075_SS1_SEM1_2024/5</t>
+          <t>CHEM08016_SV1_SEM1_2024/5, CHEM08028_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Concepts in Analytical Chemistry PGT</t>
+          <t>Chemistry 1A, Chemistry for Chemical Engineers 1A</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -3167,7 +3169,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>9, 10, 14, 15, 16, 17, 18</t>
+          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3179,17 +3181,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>E:OM3A3FTRKS-00003</t>
+          <t>E:C7PK48RUZT</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0201_01_1.08</t>
+          <t>0335_01_1.2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3198,37 +3200,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>300</v>
+        <v>44</v>
       </c>
       <c r="F47" t="n">
-        <v>307</v>
+        <v>44</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chemistry 1A - Lecture</t>
+          <t>Chemistry 3A - Workshop/Group A and Group D</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Workshop</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>CHEM08016_SV1_SEM1_2024/5, CHEM08028_SV1_SEM1_2024/5</t>
+          <t>CHEM09005_SV1_YR_2024/5, CHEM09008_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Chemistry 1A, Chemistry for Chemical Engineers 1A</t>
+          <t>Chemistry 3A, Chemistry 3A (VS1)</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
+          <t>10, 11, 12, 13</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3240,17 +3242,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>E:C7PK48RUZT</t>
+          <t>E:JXY4C6QY3W</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0335_01_1.2</t>
+          <t>0422_J_J.05</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3259,37 +3261,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="F48" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chemistry 3A - Workshop/Group A and Group D</t>
+          <t>Biological Chemistry 1A - Tutorial Group/03</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Tutorial</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>CHEM09005_SV1_YR_2024/5, CHEM09008_VV1_SEM1_2024/5</t>
+          <t>CHEM08022_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Chemistry 3A, Chemistry 3A (VS1)</t>
+          <t>Biological Chemistry 1A</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>10, 11, 12, 13</t>
+          <t>10, 12, 14, 16, 18</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3301,17 +3303,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>E:JXY4C6QY3W</t>
+          <t>E:OM3A3FTRKS-00001</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0422_J_J.03</t>
+          <t>0113_01_1.425</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3320,29 +3322,29 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>59</v>
+        <v>300</v>
       </c>
       <c r="F49" t="n">
-        <v>60</v>
+        <v>260</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Biological Chemistry 1A - Tutorial Group/03</t>
+          <t>Chemistry 1A - Lecture</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Tutorial</t>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>CHEM08022_SV1_SEM1_2024/5</t>
+          <t>CHEM08016_SV1_SEM1_2024/5, CHEM08028_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Biological Chemistry 1A</t>
+          <t>Chemistry 1A, Chemistry for Chemical Engineers 1A</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3350,7 +3352,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>10, 12, 14, 16, 18</t>
+          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3362,17 +3364,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>E:OM3A3FTRKS-00001</t>
+          <t>E:6UHQL2FU36-00002</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0201_01_1.08</t>
+          <t>0001_01_1.264</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3381,14 +3383,14 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="F50" t="n">
-        <v>307</v>
+        <v>150</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chemistry 1A - Lecture</t>
+          <t>Chemistry 2 - Lecture</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3398,12 +3400,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>CHEM08016_SV1_SEM1_2024/5, CHEM08028_SV1_SEM1_2024/5</t>
+          <t>CHEM08019_SV1_YR_2024/5, CHPH08002_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Chemistry 1A, Chemistry for Chemical Engineers 1A</t>
+          <t>Chemistry 2, Chemistry for Chemical Physics 2, Chemistry 2A</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -3411,7 +3413,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
+          <t>9, 10, 11, 12, 13, 15, 16</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3423,17 +3425,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>E:6UHQL2FU36-00002</t>
+          <t>E:RTEAVMW3MY</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0001_01_1.264</t>
+          <t>0210_00_G.04</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3442,29 +3444,29 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="F51" t="n">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chemistry 2 - Lecture</t>
+          <t>Data-driven chemistry - Q&amp;A Session</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Q&amp;A Session</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>CHEM08019_SV1_YR_2024/5, CHPH08002_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5</t>
+          <t>CHEM08031_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Chemistry 2, Chemistry for Chemical Physics 2, Chemistry 2A</t>
+          <t>Data-driven chemistry</t>
         </is>
       </c>
       <c r="K51" t="n">
@@ -3472,7 +3474,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 15, 16</t>
+          <t>10, 12, 14, 16</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3484,17 +3486,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>E:RTEAVMW3MY</t>
+          <t>E:QGSC7NW2UU-00001</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0210_00_G.04</t>
+          <t>0201_00_G.08</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Wednesday 14:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3503,29 +3505,29 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="F52" t="n">
-        <v>139</v>
+        <v>193</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Data-driven chemistry - Q&amp;A Session</t>
+          <t>Biological Chemistry 2 - Lecture</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Q&amp;A Session</t>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>CHEM08031_SV1_SEM1_2024/5</t>
+          <t>CHEM08030_VV1_SEM1_2024/5, CHEM08030_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Data-driven chemistry</t>
+          <t>Biological Chemistry 2, Biological Chemistry 2</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -3533,7 +3535,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>10, 12, 14, 16</t>
+          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3545,17 +3547,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>E:QGSC7NW2UU-00001</t>
+          <t>E:AVAG6O1HVO</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0201_00_G.08</t>
+          <t>0335_02_2.2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3564,37 +3566,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>180</v>
+        <v>44</v>
       </c>
       <c r="F53" t="n">
-        <v>193</v>
+        <v>44</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Biological Chemistry 2 - Lecture</t>
+          <t>Chemistry 3A - Workshop/Group C and Group F</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Workshop</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>CHEM08030_VV1_SEM1_2024/5, CHEM08030_SV1_SEM1_2024/5</t>
+          <t>CHEM09005_SV1_YR_2024/5, CHEM09008_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Biological Chemistry 2, Biological Chemistry 2</t>
+          <t>Chemistry 3A, Chemistry 3A (VS1)</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
+          <t>10, 13</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3606,17 +3608,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>E:AVAG6O1HVO</t>
+          <t>E:FCANK5BX72</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0335_02_2.2</t>
+          <t>0227_03_3.54</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3625,29 +3627,29 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="F54" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chemistry 3A - Workshop/Group C and Group F</t>
+          <t>Chemical Physics 3S1 - Tutorial</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Tutorial</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>CHEM09005_SV1_YR_2024/5, CHEM09008_VV1_SEM1_2024/5</t>
+          <t>CHPH09007_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Chemistry 3A, Chemistry 3A (VS1)</t>
+          <t>Chemical Physics 3S1</t>
         </is>
       </c>
       <c r="K54" t="n">
@@ -3655,7 +3657,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>10, 13</t>
+          <t>10, 11, 12, 13, 14, 15, 16, 17</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3667,17 +3669,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>E:FCANK5BX72</t>
+          <t>E:OM3A3FTRKS</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0113_01_1.26</t>
+          <t>0113_01_1.425</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3686,37 +3688,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="F55" t="n">
-        <v>10</v>
+        <v>260</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chemical Physics 3S1 - Tutorial</t>
+          <t>Chemistry 1A - Lecture</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tutorial</t>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>CHPH09007_SV1_SEM1_2024/5</t>
+          <t>CHEM08028_SV1_SEM1_2024/5, CHEM08016_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Chemical Physics 3S1</t>
+          <t>Chemistry for Chemical Engineers 1A, Chemistry 1A</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>10, 11, 12, 13, 14, 15, 16, 17</t>
+          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3728,17 +3730,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>E:OM3A3FTRKS</t>
+          <t>E:R6L7EHX8KV</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0201_01_1.08</t>
+          <t>0335_04_4.3</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Friday 15:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3747,37 +3749,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="F56" t="n">
-        <v>307</v>
+        <v>60</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chemistry 1A - Lecture</t>
+          <t>Chemistry 1A - Tutorial Group/03</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Tutorial</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>CHEM08028_SV1_SEM1_2024/5, CHEM08016_SV1_SEM1_2024/5</t>
+          <t>CHEM08016_SV1_SEM1_2024/5, CHEM08028_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Chemistry for Chemical Engineers 1A, Chemistry 1A</t>
+          <t>Chemistry 1A, Chemistry for Chemical Engineers 1A</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3789,7 +3791,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>E:R6L7EHX8KV</t>
+          <t>E:LPOUL9LTUR</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3799,7 +3801,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3815,7 +3817,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chemistry 1A - Tutorial Group/03</t>
+          <t>Chemistry 1A - Tutorial Group/02</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3834,7 +3836,7 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3850,17 +3852,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>E:LPOUL9LTUR</t>
+          <t>E:TU47N69HP7</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0422_J_J.05</t>
+          <t>0226_-1_LG.19</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3869,37 +3871,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F58" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chemistry 1A - Tutorial Group/02</t>
+          <t>Advanced Inorganic Chemistry - Lecture</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Tutorial</t>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>CHEM08016_SV1_SEM1_2024/5, CHEM08028_SV1_SEM1_2024/5</t>
+          <t>CHEM10055_SV1_SEM1_2024/5, CHEM10055_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Chemistry 1A, Chemistry for Chemical Engineers 1A</t>
+          <t>Advanced Inorganic Chemistry, Advanced Inorganic Chemistry</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19</t>
+          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -3911,17 +3913,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>E:TU47N69HP7</t>
+          <t>E:497JI377SW</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0209_02_2.01</t>
+          <t>0113_02_2.65</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3960,7 +3962,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
+          <t>9, 10, 11, 12, 13, 14, 17, 18</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -3972,17 +3974,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>E:497JI377SW</t>
+          <t>E:ZFL66JNX8S</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0209_02_2.01</t>
+          <t>0113_01M_01M.452</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3991,37 +3993,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F60" t="n">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Advanced Inorganic Chemistry - Lecture</t>
+          <t>Chemistry - Seminar</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Seminar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>CHEM10055_SV1_SEM1_2024/5, CHEM10055_VV1_SEM1_2024/5</t>
+          <t>CHEM11056_SS1_YR_2024/5, CHEM11055_SS1_YR_2024/5</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Advanced Inorganic Chemistry, Advanced Inorganic Chemistry</t>
+          <t>Chemistry/Chemical Physics Industrial Research Project, Chemistry/Chemical Physics Research Project</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 14, 17, 18</t>
+          <t>8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -4033,17 +4035,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>E:B4VNLR11TE</t>
+          <t>E:6UHQL2FU36-00001</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0225_02_2.201</t>
+          <t>0001_01_1.264</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4052,14 +4054,14 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>470</v>
+        <v>150</v>
       </c>
       <c r="F61" t="n">
-        <v>458</v>
+        <v>150</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Biological Chemistry 1A - Lecture</t>
+          <t>Chemistry 2 - Lecture</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4069,12 +4071,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>CHEM08022_SV1_SEM1_2024/5</t>
+          <t>CHEM08019_SV1_YR_2024/5, CHPH08002_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Biological Chemistry 1A</t>
+          <t>Chemistry 2, Chemistry for Chemical Physics 2, Chemistry 2A</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -4082,7 +4084,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 14, 16, 17, 18</t>
+          <t>9, 10, 11, 12, 13, 16</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4094,17 +4096,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>E:ZFL66JNX8S</t>
+          <t>E:EY2C851O7H</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0201_01_1.02</t>
+          <t>0210_00_G.04</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4113,37 +4115,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="F62" t="n">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chemistry - Seminar</t>
+          <t>Chemistry 3A - Lecture</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Seminar</t>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>CHEM11056_SS1_YR_2024/5, CHEM11055_SS1_YR_2024/5</t>
+          <t>CHEM09005_SV1_YR_2024/5, CHEM09008_VV1_SEM1_2024/5, CHPH09007_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Chemistry/Chemical Physics Industrial Research Project, Chemistry/Chemical Physics Research Project</t>
+          <t>Chemistry 3A, Chemistry 3A (VS1), Chemical Physics 3S1</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24</t>
+          <t>10, 11, 12, 13, 14, 15, 16</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -4155,17 +4157,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>E:6UHQL2FU36-00001</t>
+          <t>E:1581Q6MLYA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0001_01_1.264</t>
+          <t>0201_03_3.09</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4174,14 +4176,14 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="F63" t="n">
-        <v>150</v>
+        <v>36</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chemistry 2 - Lecture</t>
+          <t>Concepts in Materials Chemistry PGT - Lecture</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4191,12 +4193,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>CHEM08019_SV1_YR_2024/5, CHPH08002_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5</t>
+          <t>CHEM10074_SS1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Chemistry 2, Chemistry for Chemical Physics 2, Chemistry 2A</t>
+          <t>Concepts in Materials Chemistry PGT</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -4204,7 +4206,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 16</t>
+          <t>9, 10, 13, 14, 15, 16, 17, 18</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -4216,17 +4218,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>E:EY2C851O7H</t>
+          <t>E:M75U3V4PXN</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0210_00_G.04</t>
+          <t>0113_02_2.65</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Wednesday 16:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4235,14 +4237,14 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="F64" t="n">
-        <v>139</v>
+        <v>70</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chemistry 3A - Lecture</t>
+          <t>Advanced Inorganic Chemistry - Lecture</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4252,12 +4254,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>CHEM09005_SV1_YR_2024/5, CHEM09008_VV1_SEM1_2024/5, CHPH09007_SV1_SEM1_2024/5</t>
+          <t>CHEM10055_SV1_SEM1_2024/5, CHEM10055_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Chemistry 3A, Chemistry 3A (VS1), Chemical Physics 3S1</t>
+          <t>Advanced Inorganic Chemistry, Advanced Inorganic Chemistry</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -4265,7 +4267,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>10, 11, 12, 13, 14, 15, 16</t>
+          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -4277,17 +4279,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>E:1581Q6MLYA</t>
+          <t>E:KN6VKHNU5L</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0335_01_1.3</t>
+          <t>0422_J_J.05</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4296,29 +4298,29 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="F65" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Concepts in Materials Chemistry PGT - Lecture</t>
+          <t>Biological Chemistry 1A - Tutorial Group/04</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Tutorial</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>CHEM10074_SS1_SEM1_2024/5</t>
+          <t>CHEM08022_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Concepts in Materials Chemistry PGT</t>
+          <t>Biological Chemistry 1A</t>
         </is>
       </c>
       <c r="K65" t="n">
@@ -4326,7 +4328,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>9, 10, 13, 14, 15, 16, 17, 18</t>
+          <t>10, 12, 14, 16, 18</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -4338,17 +4340,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>E:M75U3V4PXN</t>
+          <t>E:7LZ7DNSFXQ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0226_-1_LG.19</t>
+          <t>0227_01_1.06</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4357,37 +4359,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F66" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Advanced Inorganic Chemistry - Lecture</t>
+          <t>Chemistry 1A - Tutorial Group/04</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Tutorial</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>CHEM10055_SV1_SEM1_2024/5, CHEM10055_VV1_SEM1_2024/5</t>
+          <t>CHEM08016_SV1_SEM1_2024/5, CHEM08028_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Advanced Inorganic Chemistry, Advanced Inorganic Chemistry</t>
+          <t>Chemistry 1A, Chemistry for Chemical Engineers 1A</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -4399,17 +4401,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>E:KN6VKHNU5L</t>
+          <t>E:LLAGOV9ZM1</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0422_J_J.05</t>
+          <t>0001_01_1.264</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4418,37 +4420,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>59</v>
+        <v>130</v>
       </c>
       <c r="F67" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Biological Chemistry 1A - Tutorial Group/04</t>
+          <t>Data-driven chemistry - Workshop</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Tutorial</t>
+          <t>Workshop</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>CHEM08022_SV1_SEM1_2024/5</t>
+          <t>CHEM08031_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Biological Chemistry 1A</t>
+          <t>Data-driven chemistry</t>
         </is>
       </c>
       <c r="K67" t="n">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>10, 12, 14, 16, 18</t>
+          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -4460,17 +4462,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>E:7LZ7DNSFXQ</t>
+          <t>E:RQLJW37MZU</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0228_-1_LG.07</t>
+          <t>0008_01_1.302</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4479,37 +4481,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="F68" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chemistry 1A - Tutorial Group/04</t>
+          <t>Concepts in Analytical Chemistry PGT - Lecture</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Tutorial</t>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>CHEM08016_SV1_SEM1_2024/5, CHEM08028_SV1_SEM1_2024/5</t>
+          <t>CHEM10075_SS1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Chemistry 1A, Chemistry for Chemical Engineers 1A</t>
+          <t>Concepts in Analytical Chemistry PGT</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19</t>
+          <t>9, 10, 14, 15, 16, 17, 18</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -4521,17 +4523,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>E:LLAGOV9ZM1</t>
+          <t>E:ZWTIQYY6AA</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0226_00_GF.14</t>
+          <t>0422_J_J.05</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4540,37 +4542,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>130</v>
+        <v>59</v>
       </c>
       <c r="F69" t="n">
-        <v>147</v>
+        <v>60</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Data-driven chemistry - Workshop</t>
+          <t>Biological Chemistry 1A - Tutorial Group/09</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Tutorial</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>CHEM08031_SV1_SEM1_2024/5</t>
+          <t>CHEM08022_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Data-driven chemistry</t>
+          <t>Biological Chemistry 1A</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>180</v>
+        <v>50</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
+          <t>10, 12, 14, 16, 18</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -4582,17 +4584,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>E:RQLJW37MZU</t>
+          <t>E:8I3PHIC8LS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0227_00_G.02</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4601,37 +4603,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F70" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Concepts in Analytical Chemistry PGT - Lecture</t>
+          <t>Chemistry 2; Chemistry 2A - Tutorial Group/03</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Tutorial</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>CHEM10075_SS1_SEM1_2024/5</t>
+          <t>CHEM08026_VV1_SEM1_2024/5, CHEM08019_SV1_YR_2024/5</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Concepts in Analytical Chemistry PGT</t>
+          <t>Chemistry 2A, Chemistry 2</t>
         </is>
       </c>
       <c r="K70" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>9, 10, 14, 15, 16, 17, 18</t>
+          <t>9, 10, 11, 13, 14, 16, 18, 19</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -4643,17 +4645,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>E:ZWTIQYY6AA</t>
+          <t>E:Y2BQIH487D-00001</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0422_J_J.05</t>
+          <t>0003_00_G.03</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4662,14 +4664,14 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="F71" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Biological Chemistry 1A - Tutorial Group/09</t>
+          <t>Chemical Physics 3S1 - Tutorial</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4679,20 +4681,20 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>CHEM08022_SV1_SEM1_2024/5</t>
+          <t>CHPH09007_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Biological Chemistry 1A</t>
+          <t>Chemical Physics 3S1</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>10, 12, 14, 16, 18</t>
+          <t>10, 11, 12</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -4704,17 +4706,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>E:8I3PHIC8LS</t>
+          <t>E:OD63917BLY</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0228_-1_LG.06</t>
+          <t>0450_01_1.60</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4723,37 +4725,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F72" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chemistry 2; Chemistry 2A - Tutorial Group/03</t>
+          <t>Concepts in Materials Chemistry PGT - Lecture</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Tutorial</t>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>CHEM08026_VV1_SEM1_2024/5, CHEM08019_SV1_YR_2024/5</t>
+          <t>CHEM10074_SS1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Chemistry 2A, Chemistry 2</t>
+          <t>Concepts in Materials Chemistry PGT</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>9, 10, 11, 13, 14, 16, 18, 19</t>
+          <t>9, 10, 13, 14, 15, 16, 17, 18</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -4765,17 +4767,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>E:Y2BQIH487D-00001</t>
+          <t>E:GXAJKXQH68</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0113_00M_00M.07</t>
+          <t>0422_J_J.05</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4784,14 +4786,14 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="F73" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chemical Physics 3S1 - Tutorial</t>
+          <t>Biological Chemistry 1A - Tutorial Group/08</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4801,20 +4803,20 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>CHPH09007_SV1_SEM1_2024/5</t>
+          <t>CHEM08022_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Chemical Physics 3S1</t>
+          <t>Biological Chemistry 1A</t>
         </is>
       </c>
       <c r="K73" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>10, 11, 12</t>
+          <t>10, 12, 14, 16, 18</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -4826,17 +4828,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>E:OD63917BLY</t>
+          <t>E:41HRRCDU1S</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0008_00_G.267</t>
+          <t>0201_04_4.12</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4845,14 +4847,14 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F74" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Concepts in Materials Chemistry PGT - Lecture</t>
+          <t>Advanced Topics in Chemical Physics - lecture</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4862,12 +4864,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>CHEM10074_SS1_SEM1_2024/5</t>
+          <t>CHPH11004_SS1_YR_2024/5</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Concepts in Materials Chemistry PGT</t>
+          <t>Advanced Topics in Chemical Physics</t>
         </is>
       </c>
       <c r="K74" t="n">
@@ -4875,7 +4877,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>9, 10, 13, 14, 15, 16, 17, 18</t>
+          <t>9, 10, 11</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -4887,17 +4889,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>E:GXAJKXQH68</t>
+          <t>E:BG2RC5SKG3</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0335_04_4.3</t>
+          <t>0228_11_11.10</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4906,14 +4908,14 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="F75" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Biological Chemistry 1A - Tutorial Group/08</t>
+          <t>Chemistry 2; Chemistry 2A - Tutorial Group/04</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4923,20 +4925,20 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>CHEM08022_SV1_SEM1_2024/5</t>
+          <t>CHEM08019_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Biological Chemistry 1A</t>
+          <t>Chemistry 2, Chemistry 2A</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>10, 12, 14, 16, 18</t>
+          <t>9, 10, 11, 13, 14, 16, 18, 19</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -4948,17 +4950,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>E:41HRRCDU1S</t>
+          <t>E:OHAXND997M</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0113_00M_00M.05</t>
+          <t>0228_-1_LG.07</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4967,37 +4969,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="F76" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Advanced Topics in Chemical Physics - lecture</t>
+          <t>Chemistry 1A - Tutorial Group/01</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Tutorial</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>CHPH11004_SS1_YR_2024/5</t>
+          <t>CHEM08016_SV1_SEM1_2024/5, CHEM08028_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Advanced Topics in Chemical Physics</t>
+          <t>Chemistry 1A, Chemistry for Chemical Engineers 1A</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>9, 10, 11</t>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -5009,17 +5011,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>E:BG2RC5SKG3</t>
+          <t>E:UQRFONNU2G</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0228_-1_LG.06</t>
+          <t>0422_J_J.05</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5028,14 +5030,14 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="F77" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chemistry 2; Chemistry 2A - Tutorial Group/04</t>
+          <t>Biological Chemistry 1A - Tutorial Group/06</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5045,20 +5047,20 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>CHEM08019_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5</t>
+          <t>CHEM08022_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Chemistry 2, Chemistry 2A</t>
+          <t>Biological Chemistry 1A</t>
         </is>
       </c>
       <c r="K77" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>9, 10, 11, 13, 14, 16, 18, 19</t>
+          <t>10, 12, 14, 16, 18</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -5070,17 +5072,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>E:OHAXND997M</t>
+          <t>E:VBCLVPOK6O</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0008_03_3.454</t>
+          <t>0005_02_2.01</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5089,37 +5091,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F78" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chemistry 1A - Tutorial Group/01</t>
+          <t>Advanced Organic Chemistry - Lecture</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Tutorial</t>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>CHEM08016_SV1_SEM1_2024/5, CHEM08028_SV1_SEM1_2024/5</t>
+          <t>CHEM10057_SV1_SEM1_2024/5, CHEM10057_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Chemistry 1A, Chemistry for Chemical Engineers 1A</t>
+          <t>Advanced Organic Chemistry, Advanced Organic Chemistry</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19</t>
+          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -5131,17 +5133,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>E:UQRFONNU2G</t>
+          <t>E:GYIC11DXGU</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0422_J_J.03</t>
+          <t>0300_00_NG.02</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5150,14 +5152,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="F79" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Biological Chemistry 1A - Tutorial Group/06</t>
+          <t>Chemistry 2; Chemistry 2A - Tutorial Group/02</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5167,20 +5169,20 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>CHEM08022_SV1_SEM1_2024/5</t>
+          <t>CHEM08019_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Biological Chemistry 1A</t>
+          <t>Chemistry 2, Chemistry 2A</t>
         </is>
       </c>
       <c r="K79" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>10, 12, 14, 16, 18</t>
+          <t>9, 10, 11, 13, 14, 16, 18, 19</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -5192,17 +5194,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>E:VBCLVPOK6O</t>
+          <t>E:QGSC7NW2UU</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0005_01_1.01</t>
+          <t>0201_00_G.06</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5211,14 +5213,14 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="F80" t="n">
-        <v>65</v>
+        <v>193</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Advanced Organic Chemistry - Lecture</t>
+          <t>Biological Chemistry 2 - Lecture</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5228,12 +5230,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>CHEM10057_SV1_SEM1_2024/5, CHEM10057_VV1_SEM1_2024/5</t>
+          <t>CHEM08030_SV1_SEM1_2024/5, CHEM08030_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Advanced Organic Chemistry, Advanced Organic Chemistry</t>
+          <t>Biological Chemistry 2, Biological Chemistry 2</t>
         </is>
       </c>
       <c r="K80" t="n">
@@ -5253,17 +5255,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>E:GYIC11DXGU</t>
+          <t>E:Y2BQIH487D</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0112_-1_B.01</t>
+          <t>0008_02_2.418</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5272,14 +5274,14 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F81" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chemistry 2; Chemistry 2A - Tutorial Group/02</t>
+          <t>Chemical Physics 3S1 - Tutorial</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5289,12 +5291,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>CHEM08019_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5</t>
+          <t>CHPH09007_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Chemistry 2, Chemistry 2A</t>
+          <t>Chemical Physics 3S1</t>
         </is>
       </c>
       <c r="K81" t="n">
@@ -5302,7 +5304,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>9, 10, 11, 13, 14, 16, 18, 19</t>
+          <t>10, 11, 12</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -5314,17 +5316,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>E:QGSC7NW2UU</t>
+          <t>E:DUK4R8PVEB</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0201_00_G.08</t>
+          <t>0112_-1_B.06</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5333,14 +5335,14 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>180</v>
+        <v>25</v>
       </c>
       <c r="F82" t="n">
-        <v>193</v>
+        <v>25</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Biological Chemistry 2 - Lecture</t>
+          <t>Concepts in Analytical Chemistry PGT - Lecture</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5350,12 +5352,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>CHEM08030_SV1_SEM1_2024/5, CHEM08030_VV1_SEM1_2024/5</t>
+          <t>CHEM10075_SS1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Biological Chemistry 2, Biological Chemistry 2</t>
+          <t>Concepts in Analytical Chemistry PGT</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -5363,7 +5365,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
+          <t>9, 10, 13, 14, 15, 16, 17, 18</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -5375,17 +5377,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>E:Y2BQIH487D</t>
+          <t>E:WQ4RRVBG5I</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0113_00M_00M.03</t>
+          <t>0450_01_1.50</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5394,37 +5396,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F83" t="n">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chemical Physics 3S1 - Tutorial</t>
+          <t>Sustainable Chemistry - Lecture</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Tutorial</t>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>CHPH09007_SV1_SEM1_2024/5</t>
+          <t>CHEM10023_SV1_SEM1_2024/5, CHEM10023_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Chemical Physics 3S1</t>
+          <t>Sustainable Chemistry Level 10, Sustainable Chemistry Level 10</t>
         </is>
       </c>
       <c r="K83" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>10, 11, 12</t>
+          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -5436,17 +5438,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>E:DUK4R8PVEB</t>
+          <t>E:VQF6QGMEYU</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0422_J_J.05</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5455,29 +5457,29 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="F84" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Concepts in Analytical Chemistry PGT - Lecture</t>
+          <t>Biological Chemistry 1A - Tutorial Group/01</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Tutorial</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>CHEM10075_SS1_SEM1_2024/5</t>
+          <t>CHEM08022_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Concepts in Analytical Chemistry PGT</t>
+          <t>Biological Chemistry 1A</t>
         </is>
       </c>
       <c r="K84" t="n">
@@ -5485,7 +5487,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>9, 10, 13, 14, 15, 16, 17, 18</t>
+          <t>10, 12, 14, 16, 18</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -5497,17 +5499,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>E:WQ4RRVBG5I</t>
+          <t>E:AJ8W2EPRC9</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0113_00_G.03</t>
+          <t>0450_01_1.40</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5519,11 +5521,11 @@
         <v>50</v>
       </c>
       <c r="F85" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sustainable Chemistry - Lecture</t>
+          <t>Advanced Physical Chemistry - Lecture</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5533,12 +5535,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>CHEM10023_SV1_SEM1_2024/5, CHEM10023_VV1_SEM1_2024/5</t>
+          <t>CHEM10056_SV1_SEM1_2024/5, CHEM10056_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Sustainable Chemistry Level 10, Sustainable Chemistry Level 10</t>
+          <t>Advanced Physical Chemistry, Advanced Physical Chemistry</t>
         </is>
       </c>
       <c r="K85" t="n">
@@ -5558,17 +5560,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>E:VQF6QGMEYU</t>
+          <t>E:KGO4SIHJ7G</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0335_04_4.3</t>
+          <t>0450_01_1.40</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5577,29 +5579,29 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="F86" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Biological Chemistry 1A - Tutorial Group/01</t>
+          <t>Advanced Physical Chemistry - Lecture</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Tutorial</t>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>CHEM08022_SV1_SEM1_2024/5</t>
+          <t>CHEM10056_SV1_SEM1_2024/5, CHEM10056_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Biological Chemistry 1A</t>
+          <t>Advanced Physical Chemistry, Advanced Physical Chemistry</t>
         </is>
       </c>
       <c r="K86" t="n">
@@ -5607,7 +5609,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>10, 12, 14, 16, 18</t>
+          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -5619,17 +5621,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>E:B4VNLR11TE-00002</t>
+          <t>E:KLP9U62SYM-00001</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0225_02_2.201</t>
+          <t>0210_00_G.04</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5638,14 +5640,14 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>470</v>
+        <v>130</v>
       </c>
       <c r="F87" t="n">
-        <v>458</v>
+        <v>139</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Biological Chemistry 1A - Lecture</t>
+          <t>Chemistry 3B - Lecture</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5655,12 +5657,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>CHEM08022_SV1_SEM1_2024/5</t>
+          <t>CHEM09006_SV1_YR_2024/5, CHEM09009_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Biological Chemistry 1A</t>
+          <t>Chemistry 3B, Chemistry 3B (VS1)</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -5668,7 +5670,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
+          <t>9, 10, 11, 13, 14, 15, 16, 17, 18</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -5680,17 +5682,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>E:AJ8W2EPRC9</t>
+          <t>E:IA72KGXKBL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0113_00_G.03</t>
+          <t>0422_J_J.05</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Friday 15:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5699,29 +5701,29 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="F88" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Advanced Physical Chemistry - Lecture</t>
+          <t>Biological Chemistry 1A - Tutorial Group/05</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Tutorial</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>CHEM10056_SV1_SEM1_2024/5, CHEM10056_VV1_SEM1_2024/5</t>
+          <t>CHEM08022_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Advanced Physical Chemistry, Advanced Physical Chemistry</t>
+          <t>Biological Chemistry 1A</t>
         </is>
       </c>
       <c r="K88" t="n">
@@ -5729,7 +5731,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
+          <t>10, 12, 14, 16, 18</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -5741,17 +5743,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>E:KGO4SIHJ7G</t>
+          <t>E:R9JA5E7SPU</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0113_00_G.03</t>
+          <t>0008_01_1.302</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5760,14 +5762,14 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F89" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Advanced Physical Chemistry - Lecture</t>
+          <t>Concepts in Medicinal and Biological Chemistry PGT - Lecture</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5777,12 +5779,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>CHEM10056_SV1_SEM1_2024/5, CHEM10056_VV1_SEM1_2024/5</t>
+          <t>CHEM10073_SS1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Advanced Physical Chemistry, Advanced Physical Chemistry</t>
+          <t>Concepts in Medicinal and Biological Chemistry PGT</t>
         </is>
       </c>
       <c r="K89" t="n">
@@ -5802,17 +5804,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>E:KLP9U62SYM-00001</t>
+          <t>E:OX2S4TEQMO</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0210_00_G.04</t>
+          <t>0422_J_J.05</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5821,37 +5823,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="F90" t="n">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chemistry 3B - Lecture</t>
+          <t>Chemistry 1A - Tutorial Group/06</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Tutorial</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>CHEM09006_SV1_YR_2024/5, CHEM09009_VV1_SEM1_2024/5</t>
+          <t>CHEM08016_SV1_SEM1_2024/5, CHEM08028_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Chemistry 3B, Chemistry 3B (VS1)</t>
+          <t>Chemistry 1A, Chemistry for Chemical Engineers 1A</t>
         </is>
       </c>
       <c r="K90" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>9, 10, 11, 13, 14, 15, 16, 17, 18</t>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -5863,17 +5865,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>E:B4VNLR11TE-00001</t>
+          <t>E:KDYFU6DE8Q</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0225_02_2.201</t>
+          <t>0113_01M_01M.467</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5882,14 +5884,14 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>470</v>
+        <v>25</v>
       </c>
       <c r="F91" t="n">
-        <v>458</v>
+        <v>25</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Biological Chemistry 1A - Lecture</t>
+          <t>Concepts in Medicinal and Biological Chemistry PGT - Lecture</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5899,12 +5901,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>CHEM08022_SV1_SEM1_2024/5</t>
+          <t>CHEM10073_SS1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Biological Chemistry 1A</t>
+          <t>Concepts in Medicinal and Biological Chemistry PGT</t>
         </is>
       </c>
       <c r="K91" t="n">
@@ -5924,17 +5926,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>E:IA72KGXKBL</t>
+          <t>E:QVUUCAXNXZ</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0335_04_4.3</t>
+          <t>0131_04_4.07</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5943,29 +5945,29 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="F92" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Biological Chemistry 1A - Tutorial Group/05</t>
+          <t>Optional Courses in Chemistry PGT - Lecture</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Tutorial</t>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>CHEM08022_SV1_SEM1_2024/5</t>
+          <t>CHEM11081_SS1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Biological Chemistry 1A</t>
+          <t>Optional Courses in Chemistry PGT</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -5973,7 +5975,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>10, 12, 14, 16, 18</t>
+          <t>10, 11, 12, 14, 15, 16</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -5985,17 +5987,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>E:R9JA5E7SPU</t>
+          <t>E:8TJSUV4VTJ</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0227_03_3.39</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6004,37 +6006,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F93" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Concepts in Medicinal and Biological Chemistry PGT - Lecture</t>
+          <t>Chemistry for Chemical Physics 2 - Tutorial Group/05</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Tutorial</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>CHEM10073_SS1_SEM1_2024/5</t>
+          <t>CHPH08002_SV1_YR_2024/5</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Concepts in Medicinal and Biological Chemistry PGT</t>
+          <t>Chemistry for Chemical Physics 2</t>
         </is>
       </c>
       <c r="K93" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
+          <t>9, 10, 11, 13, 14, 16, 18, 19</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -6046,12 +6048,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>E:OX2S4TEQMO</t>
+          <t>E:5QRPSXF6PJ</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0422_J_J.05</t>
+          <t>0210_-1_B.51</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6065,37 +6067,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F94" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chemistry 1A - Tutorial Group/06</t>
+          <t>Advanced Organic Chemistry - Lecture</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Tutorial</t>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>CHEM08016_SV1_SEM1_2024/5, CHEM08028_SV1_SEM1_2024/5</t>
+          <t>CHEM10057_SV1_SEM1_2024/5, CHEM10057_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Chemistry 1A, Chemistry for Chemical Engineers 1A</t>
+          <t>Advanced Organic Chemistry, Advanced Organic Chemistry</t>
         </is>
       </c>
       <c r="K94" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19</t>
+          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -6107,17 +6109,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>E:KDYFU6DE8Q</t>
+          <t>E:ODZQVAW11P</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0450_01_1.50</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6126,14 +6128,14 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F95" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Concepts in Medicinal and Biological Chemistry PGT - Lecture</t>
+          <t>Sustainable Chemistry - Lecture</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6143,12 +6145,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>CHEM10073_SS1_SEM1_2024/5</t>
+          <t>CHEM10023_SV1_SEM1_2024/5, CHEM10023_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Concepts in Medicinal and Biological Chemistry PGT</t>
+          <t>Sustainable Chemistry Level 10, Sustainable Chemistry Level 10</t>
         </is>
       </c>
       <c r="K95" t="n">
@@ -6168,17 +6170,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>E:QVUUCAXNXZ</t>
+          <t>E:W7V3PKJ7E5</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0201_01_1.02</t>
+          <t>0201_04_4.12</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6187,14 +6189,14 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="F96" t="n">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Optional Courses in Chemistry PGT - Lecture</t>
+          <t>Concepts in Materials Chemistry PGT - Lecture</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6204,12 +6206,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>CHEM11081_SS1_SEM1_2024/5</t>
+          <t>CHEM10074_SS1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Optional Courses in Chemistry PGT</t>
+          <t>Concepts in Materials Chemistry PGT</t>
         </is>
       </c>
       <c r="K96" t="n">
@@ -6217,7 +6219,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>10, 11, 12, 14, 15, 16</t>
+          <t>9, 10, 13, 14, 15, 16, 17, 18</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -6229,17 +6231,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>E:8TJSUV4VTJ</t>
+          <t>E:59MFO7JHWR</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0254_01_1.03</t>
+          <t>0210_00_G.04</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6248,37 +6250,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>15</v>
+        <v>130</v>
       </c>
       <c r="F97" t="n">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Chemistry for Chemical Physics 2 - Tutorial Group/05</t>
+          <t>Chemistry 3A - Lecture</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Tutorial</t>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>CHPH08002_SV1_YR_2024/5</t>
+          <t>CHEM09005_SV1_YR_2024/5, CHEM09008_VV1_SEM1_2024/5, CHPH09007_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Chemistry for Chemical Physics 2</t>
+          <t>Chemistry 3A, Chemistry 3A (VS1), Chemical Physics 3S1</t>
         </is>
       </c>
       <c r="K97" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>9, 10, 11, 13, 14, 16, 18, 19</t>
+          <t>9, 10, 11, 12, 13, 14, 15, 16</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -6290,17 +6292,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>E:5QRPSXF6PJ</t>
+          <t>E:GBC28B6YLF</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0210_-1_B.51</t>
+          <t>0226_00_GF.14</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6309,14 +6311,14 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="F98" t="n">
-        <v>65</v>
+        <v>147</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Advanced Organic Chemistry - Lecture</t>
+          <t>Chemistry 3A - Lecture</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6326,12 +6328,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>CHEM10057_SV1_SEM1_2024/5, CHEM10057_VV1_SEM1_2024/5</t>
+          <t>CHEM09005_SV1_YR_2024/5, CHEM09008_VV1_SEM1_2024/5, CHPH09007_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Advanced Organic Chemistry, Advanced Organic Chemistry</t>
+          <t>Chemistry 3A, Chemistry 3A (VS1), Chemical Physics 3S1</t>
         </is>
       </c>
       <c r="K98" t="n">
@@ -6339,7 +6341,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
+          <t>9, 10, 11, 13, 14, 15</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -6351,17 +6353,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>E:ODZQVAW11P</t>
+          <t>E:C7GT7SQL4X</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0300_00_NG.01</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Friday 15:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6370,37 +6372,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="F99" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sustainable Chemistry - Lecture</t>
+          <t>Chemistry 2; Chemistry 2A - Tutorial Group/01</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Tutorial</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>CHEM10023_SV1_SEM1_2024/5, CHEM10023_VV1_SEM1_2024/5</t>
+          <t>CHEM08019_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Sustainable Chemistry Level 10, Sustainable Chemistry Level 10</t>
+          <t>Chemistry 2, Chemistry 2A</t>
         </is>
       </c>
       <c r="K99" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 14, 15, 16, 17, 18</t>
+          <t>9, 10, 11, 13, 14, 16, 18, 19</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -6412,17 +6414,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>E:W7V3PKJ7E5</t>
+          <t>E:WI3SCGO928</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0210_00_G.04</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 17:00</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6431,14 +6433,14 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="F100" t="n">
-        <v>30</v>
+        <v>139</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Concepts in Materials Chemistry PGT - Lecture</t>
+          <t>Chemistry 3A - Lecture</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6448,12 +6450,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>CHEM10074_SS1_SEM1_2024/5</t>
+          <t>CHEM09005_SV1_YR_2024/5, CHEM09008_VV1_SEM1_2024/5, CHPH09007_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Concepts in Materials Chemistry PGT</t>
+          <t>Chemistry 3A, Chemistry 3A (VS1), Chemical Physics 3S1</t>
         </is>
       </c>
       <c r="K100" t="n">
@@ -6461,7 +6463,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>9, 10, 13, 14, 15, 16, 17, 18</t>
+          <t>9, 10, 11, 12, 13, 14, 15</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -6473,57 +6475,51 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>E:59MFO7JHWR</t>
+          <t>E:ZRYWL8KT1Q</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0210_00_G.04</t>
+          <t>0654_-1_LG.01</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>milp</t>
-        </is>
-      </c>
-      <c r="E101" t="n">
-        <v>130</v>
-      </c>
-      <c r="F101" t="n">
-        <v>139</v>
-      </c>
+          <t>fixed_non_vet</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chemistry 3A - Lecture</t>
+          <t>Advanced Topics in Chemical Physics - Machine Learning Workshop</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Computer Workshop</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>CHEM09005_SV1_YR_2024/5, CHEM09008_VV1_SEM1_2024/5, CHPH09007_SV1_SEM1_2024/5</t>
+          <t>CHPH11004_SS1_YR_2024/5</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Chemistry 3A, Chemistry 3A (VS1), Chemical Physics 3S1</t>
+          <t>Advanced Topics in Chemical Physics</t>
         </is>
       </c>
       <c r="K101" t="n">
-        <v>50</v>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>9, 10, 11, 12, 13, 14, 15, 16</t>
-        </is>
+        <v>230</v>
+      </c>
+      <c r="L101" t="n">
+        <v>9</v>
       </c>
       <c r="M101" t="inlineStr">
         <is>
@@ -6534,56 +6530,54 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>E:GBC28B6YLF</t>
+          <t>E:YXP6H35VNQ</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0210_00_G.04</t>
+          <t>0632_00_G.A04</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Thursday 11:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>milp</t>
+          <t>fixed_non_vet</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>130</v>
-      </c>
-      <c r="F102" t="n">
-        <v>139</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chemistry 3A - Lecture</t>
+          <t>Chemistry 3P - Lab (P)/Group D</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Laboratory</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>CHEM09005_SV1_YR_2024/5, CHEM09008_VV1_SEM1_2024/5, CHPH09007_SV1_SEM1_2024/5</t>
+          <t>CHEM09007_SV1_YR_2024/5</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Chemistry 3A, Chemistry 3A (VS1), Chemical Physics 3S1</t>
+          <t>Chemistry 3P Practical and Transferable Skills</t>
         </is>
       </c>
       <c r="K102" t="n">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>9, 10, 11, 13, 14, 15</t>
+          <t>10, 11, 12, 13, 14, 15</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -6595,56 +6589,54 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>E:C7GT7SQL4X</t>
+          <t>E:7XGWB5ZFPY</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0228_-1_LG.06</t>
+          <t>0632_00_G.A07</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>milp</t>
+          <t>fixed_non_vet</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>34</v>
-      </c>
-      <c r="F103" t="n">
-        <v>35</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Chemistry 2; Chemistry 2A - Tutorial Group/01</t>
+          <t>Laboratory Techniques 1 Chemistry PGT - Laboratory/Analytical Group</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Tutorial</t>
+          <t>Laboratory</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>CHEM08019_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5</t>
+          <t>CHEM11082_SS1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Chemistry 2, Chemistry 2A</t>
+          <t>Laboratory Techniques 1 Chemistry PGT</t>
         </is>
       </c>
       <c r="K103" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>9, 10, 11, 13, 14, 16, 18, 19</t>
+          <t>9, 10, 11, 13, 14, 15, 16, 17, 18</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -6656,52 +6648,50 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>E:WI3SCGO928</t>
+          <t>E:9ES4C2GEUA</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0210_00_G.04</t>
+          <t>0632_01_1.A10</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>milp</t>
+          <t>fixed_non_vet</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>130</v>
-      </c>
-      <c r="F104" t="n">
-        <v>139</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Chemistry 3A - Lecture</t>
+          <t>Chemistry 3P - Lab (O)/Group A</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Laboratory</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>CHEM09005_SV1_YR_2024/5, CHEM09008_VV1_SEM1_2024/5, CHPH09007_SV1_SEM1_2024/5</t>
+          <t>CHEM09007_SV1_YR_2024/5</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Chemistry 3A, Chemistry 3A (VS1), Chemical Physics 3S1</t>
+          <t>Chemistry 3P Practical and Transferable Skills</t>
         </is>
       </c>
       <c r="K104" t="n">
-        <v>50</v>
+        <v>170</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -6717,17 +6707,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>E:ZRYWL8KT1Q</t>
+          <t>E:2KCA425N9F</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0654_-1_LG.01</t>
+          <t>0632_00_G.A07</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6735,33 +6725,37 @@
           <t>fixed_non_vet</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
+      <c r="E105" t="n">
+        <v>25</v>
+      </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Advanced Topics in Chemical Physics - Machine Learning Workshop</t>
+          <t>Laboratory Techniques 1 Chemistry PGT - Laboratory/Materials Group</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Computer Workshop</t>
+          <t>Laboratory</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>CHPH11004_SS1_YR_2024/5</t>
+          <t>CHEM11082_SS1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Advanced Topics in Chemical Physics</t>
+          <t>Laboratory Techniques 1 Chemistry PGT</t>
         </is>
       </c>
       <c r="K105" t="n">
-        <v>230</v>
-      </c>
-      <c r="L105" t="n">
-        <v>9</v>
+        <v>170</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>9, 10, 11, 13, 14, 15, 16, 17, 18</t>
+        </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
@@ -6772,17 +6766,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>E:YXP6H35VNQ</t>
+          <t>E:Z5YS3SEMPX</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0632_00_G.A04</t>
+          <t>0639_03_3.03</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6791,12 +6785,12 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chemistry 3P - Lab (P)/Group D</t>
+          <t>Biological Chemistry 2 - Laboratory/White Group</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6806,20 +6800,20 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>CHEM09007_SV1_YR_2024/5</t>
+          <t>CHEM08030_VV1_SEM1_2024/5, CHEM08030_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Chemistry 3P Practical and Transferable Skills</t>
+          <t>Biological Chemistry 2, Biological Chemistry 2</t>
         </is>
       </c>
       <c r="K106" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>10, 11, 12, 13, 14, 15</t>
+          <t>10, 12, 14, 16</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -6831,17 +6825,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>E:7XGWB5ZFPY</t>
+          <t>E:UXYD57AI9S-00001</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0632_00_G.A07</t>
+          <t>0632_01_1.A04</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6850,12 +6844,12 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Laboratory Techniques 1 Chemistry PGT - Laboratory/Analytical Group</t>
+          <t>Chemistry 2 - Inorganic Lab Fpm</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6865,20 +6859,20 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>CHEM11082_SS1_SEM1_2024/5</t>
+          <t>CHEM08019_SV1_YR_2024/5, CHPH08002_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Laboratory Techniques 1 Chemistry PGT</t>
+          <t>Chemistry 2, Chemistry for Chemical Physics 2, Chemistry 2A</t>
         </is>
       </c>
       <c r="K107" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>9, 10, 11, 13, 14, 15, 16, 17, 18</t>
+          <t>10, 11, 12, 13, 14, 15</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -6890,17 +6884,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>E:9ES4C2GEUA</t>
+          <t>E:FCMO2C3WQA</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0632_01_1.A10</t>
+          <t>0632_01_1.A04</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6909,12 +6903,12 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Chemistry 3P - Lab (O)/Group A</t>
+          <t>Chemistry 2 - Inorganic Lab/Mpm</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -6924,12 +6918,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>CHEM09007_SV1_YR_2024/5</t>
+          <t>CHPH08002_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5, CHEM08019_SV1_YR_2024/5</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Chemistry 3P Practical and Transferable Skills</t>
+          <t>Chemistry for Chemical Physics 2, Chemistry 2A, Chemistry 2</t>
         </is>
       </c>
       <c r="K108" t="n">
@@ -6937,7 +6931,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 14, 15</t>
+          <t>10, 11, 12, 13, 14, 15</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -6949,17 +6943,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>E:2KCA425N9F</t>
+          <t>E:D9Z92AU3FL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0632_00_G.A07</t>
+          <t>0632_01_1.A04</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6968,12 +6962,12 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Laboratory Techniques 1 Chemistry PGT - Laboratory/Materials Group</t>
+          <t>Chemistry 2 - Inorganic Lab/Mpm</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -6983,12 +6977,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>CHEM11082_SS1_SEM1_2024/5</t>
+          <t>CHEM08019_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5, CHPH08002_SV1_YR_2024/5</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Laboratory Techniques 1 Chemistry PGT</t>
+          <t>Chemistry 2, Chemistry 2A, Chemistry for Chemical Physics 2</t>
         </is>
       </c>
       <c r="K109" t="n">
@@ -6996,7 +6990,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>9, 10, 11, 13, 14, 15, 16, 17, 18</t>
+          <t>10, 11, 12, 13, 14, 15</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -7008,17 +7002,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>E:Z5YS3SEMPX</t>
+          <t>E:CPRK4LLZE5</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0639_03_3.03</t>
+          <t>0632_01_1.A04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -7027,12 +7021,12 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Biological Chemistry 2 - Laboratory/White Group</t>
+          <t>Chemistry 2 - Inorganic Lab/Wam</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7042,20 +7036,20 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>CHEM08030_VV1_SEM1_2024/5, CHEM08030_SV1_SEM1_2024/5</t>
+          <t>CHEM08019_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5, CHPH08002_SV1_YR_2024/5</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Biological Chemistry 2, Biological Chemistry 2</t>
+          <t>Chemistry 2, Chemistry 2A, Chemistry for Chemical Physics 2</t>
         </is>
       </c>
       <c r="K110" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>10, 12, 14, 16</t>
+          <t>10, 11, 12, 13, 14, 15</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -7067,7 +7061,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>E:UXYD57AI9S-00001</t>
+          <t>E:1XTXK8TVXU</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7077,7 +7071,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -7091,7 +7085,7 @@
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chemistry 2 - Inorganic Lab Fpm</t>
+          <t>Chemistry 2 - Inorganic Lab/Fam</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7101,16 +7095,16 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>CHEM08019_SV1_YR_2024/5, CHPH08002_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5</t>
+          <t>CHPH08002_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5, CHEM08019_SV1_YR_2024/5</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Chemistry 2, Chemistry for Chemical Physics 2, Chemistry 2A</t>
+          <t>Chemistry for Chemical Physics 2, Chemistry 2A, Chemistry 2</t>
         </is>
       </c>
       <c r="K111" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -7126,17 +7120,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>E:FCMO2C3WQA</t>
+          <t>E:ID28MUZ3NH</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0632_01_1.A04</t>
+          <t>0632_00_G.A07</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -7145,12 +7139,12 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Chemistry 2 - Inorganic Lab/Mpm</t>
+          <t>Laboratory Techniques 1 Chemistry PGT - Laboratory/Medicinal &amp; Biological Group</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7160,20 +7154,20 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>CHPH08002_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5, CHEM08019_SV1_YR_2024/5</t>
+          <t>CHEM11082_SS1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Chemistry for Chemical Physics 2, Chemistry 2A, Chemistry 2</t>
+          <t>Laboratory Techniques 1 Chemistry PGT</t>
         </is>
       </c>
       <c r="K112" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>10, 11, 12, 13, 14, 15</t>
+          <t>9, 10, 11, 13, 14, 15, 16, 17, 18</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -7185,17 +7179,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>E:D9Z92AU3FL</t>
+          <t>E:AQVHULQ66R</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0632_01_1.A04</t>
+          <t>0632_00_G.A04</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7204,12 +7198,12 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Chemistry 2 - Inorganic Lab/Mpm</t>
+          <t>Chemistry 3P - Lab (P)/Group F</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7219,12 +7213,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>CHEM08019_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5, CHPH08002_SV1_YR_2024/5</t>
+          <t>CHEM09007_SV1_YR_2024/5</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Chemistry 2, Chemistry 2A, Chemistry for Chemical Physics 2</t>
+          <t>Chemistry 3P Practical and Transferable Skills</t>
         </is>
       </c>
       <c r="K113" t="n">
@@ -7244,17 +7238,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>E:CPRK4LLZE5</t>
+          <t>E:BCF2JWYEVG</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0632_01_1.A04</t>
+          <t>0639_03_3.03</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7263,12 +7257,12 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Chemistry 2 - Inorganic Lab/Wam</t>
+          <t>Biological Chemistry 2 - Laboratory/Orange Group</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7278,20 +7272,20 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>CHEM08019_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5, CHPH08002_SV1_YR_2024/5</t>
+          <t>CHEM08030_VV1_SEM1_2024/5, CHEM08030_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Chemistry 2, Chemistry 2A, Chemistry for Chemical Physics 2</t>
+          <t>Biological Chemistry 2, Biological Chemistry 2</t>
         </is>
       </c>
       <c r="K114" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>10, 11, 12, 13, 14, 15</t>
+          <t>10, 12, 14, 16</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -7303,17 +7297,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>E:1XTXK8TVXU</t>
+          <t>E:IU9A9GAIJM</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0632_01_1.A04</t>
+          <t>0632_01_1.A10</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7322,12 +7316,12 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Chemistry 2 - Inorganic Lab/Fam</t>
+          <t>Chemistry 3P - Lab (O)/Group C</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7337,12 +7331,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>CHPH08002_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5, CHEM08019_SV1_YR_2024/5</t>
+          <t>CHEM09007_SV1_YR_2024/5</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Chemistry for Chemical Physics 2, Chemistry 2A, Chemistry 2</t>
+          <t>Chemistry 3P Practical and Transferable Skills</t>
         </is>
       </c>
       <c r="K115" t="n">
@@ -7350,7 +7344,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>10, 11, 12, 13, 14, 15</t>
+          <t>9, 10, 11, 12, 13, 14, 15</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -7362,17 +7356,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>E:ID28MUZ3NH</t>
+          <t>E:ODMKRN3NF1</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0632_00_G.A07</t>
+          <t>0632_01_1.A04</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7381,12 +7375,12 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Laboratory Techniques 1 Chemistry PGT - Laboratory/Medicinal &amp; Biological Group</t>
+          <t>Chemistry 2 - Inorganic Lab/Tam</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7396,12 +7390,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>CHEM11082_SS1_SEM1_2024/5</t>
+          <t>CHEM08019_SV1_YR_2024/5, CHPH08002_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Laboratory Techniques 1 Chemistry PGT</t>
+          <t>Chemistry 2, Chemistry for Chemical Physics 2, Chemistry 2A</t>
         </is>
       </c>
       <c r="K116" t="n">
@@ -7409,7 +7403,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>9, 10, 11, 13, 14, 15, 16, 17, 18</t>
+          <t>10, 11, 12, 13, 14, 15</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -7421,7 +7415,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>E:AQVHULQ66R</t>
+          <t>E:F8OSROHCOL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7431,7 +7425,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7445,7 +7439,7 @@
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Chemistry 3P - Lab (P)/Group F</t>
+          <t>Chemistry 3P - Lab (P)/Group E</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7480,7 +7474,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>E:BCF2JWYEVG</t>
+          <t>E:Z8T455UA53</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7504,7 +7498,7 @@
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Biological Chemistry 2 - Laboratory/Orange Group</t>
+          <t>Biological Chemistry 2 - Laboratory/Blue Group</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7514,7 +7508,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>CHEM08030_VV1_SEM1_2024/5, CHEM08030_SV1_SEM1_2024/5</t>
+          <t>CHEM08030_SV1_SEM1_2024/5, CHEM08030_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7539,17 +7533,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>E:IU9A9GAIJM</t>
+          <t>E:ADCRSQUC3Q</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0632_01_1.A10</t>
+          <t>0632_00_G.A07</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7558,12 +7552,12 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Chemistry 3P - Lab (O)/Group C</t>
+          <t>Laboratory Techniques 1 Chemistry PGT - Laboratory/Medicinal &amp; Biological Group</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7573,12 +7567,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>CHEM09007_SV1_YR_2024/5</t>
+          <t>CHEM11082_SS1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Chemistry 3P Practical and Transferable Skills</t>
+          <t>Laboratory Techniques 1 Chemistry PGT</t>
         </is>
       </c>
       <c r="K119" t="n">
@@ -7586,7 +7580,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 14, 15</t>
+          <t>9, 10, 11, 13, 14, 15, 16, 17, 18</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -7598,17 +7592,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>E:ODMKRN3NF1</t>
+          <t>E:NP3NF6R86P</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0632_01_1.A04</t>
+          <t>0639_03_3.03</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7617,12 +7611,12 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Chemistry 2 - Inorganic Lab/Tam</t>
+          <t>Biological Chemistry 2 - Laboratory/Red Group</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7632,20 +7626,20 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>CHEM08019_SV1_YR_2024/5, CHPH08002_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5</t>
+          <t>CHEM08030_SV1_SEM1_2024/5, CHEM08030_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Chemistry 2, Chemistry for Chemical Physics 2, Chemistry 2A</t>
+          <t>Biological Chemistry 2, Biological Chemistry 2</t>
         </is>
       </c>
       <c r="K120" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>10, 11, 12, 13, 14, 15</t>
+          <t>10, 12, 14, 16</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -7657,7 +7651,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>E:F8OSROHCOL</t>
+          <t>E:HP814ZRIZI</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7667,7 +7661,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7681,7 +7675,7 @@
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Chemistry 3P - Lab (P)/Group E</t>
+          <t>Chemistry 3P - Lab (P)/Group D</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7716,17 +7710,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>E:Z8T455UA53</t>
+          <t>E:WHML9Z9JRE</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0639_03_3.03</t>
+          <t>0632_01_1.A10</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7735,12 +7729,12 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Biological Chemistry 2 - Laboratory/Blue Group</t>
+          <t>Chemistry 3P - Lab (O)/Group A</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7750,12 +7744,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>CHEM08030_SV1_SEM1_2024/5, CHEM08030_VV1_SEM1_2024/5</t>
+          <t>CHEM09007_SV1_YR_2024/5</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Biological Chemistry 2, Biological Chemistry 2</t>
+          <t>Chemistry 3P Practical and Transferable Skills</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -7763,7 +7757,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>10, 12, 14, 16</t>
+          <t>9, 10, 11, 12, 13, 14, 15</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -7775,17 +7769,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>E:ADCRSQUC3Q</t>
+          <t>E:EJIU85QYHX</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0632_00_G.A07</t>
+          <t>0632_00_G.A04</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7794,12 +7788,12 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Laboratory Techniques 1 Chemistry PGT - Laboratory/Medicinal &amp; Biological Group</t>
+          <t>Chemistry 3P - Lab (P)/Group E</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7809,12 +7803,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>CHEM11082_SS1_SEM1_2024/5</t>
+          <t>CHEM09007_SV1_YR_2024/5</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Laboratory Techniques 1 Chemistry PGT</t>
+          <t>Chemistry 3P Practical and Transferable Skills</t>
         </is>
       </c>
       <c r="K123" t="n">
@@ -7822,7 +7816,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>9, 10, 11, 13, 14, 15, 16, 17, 18</t>
+          <t>10, 11, 12, 13, 14, 15</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -7834,17 +7828,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>E:NP3NF6R86P</t>
+          <t>E:34MPVI6AF1</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0639_03_3.03</t>
+          <t>0632_01_1.A04</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7853,12 +7847,12 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Biological Chemistry 2 - Laboratory/Red Group</t>
+          <t>Chemistry 2 - Inorganic Lab/Fam</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7868,20 +7862,20 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>CHEM08030_SV1_SEM1_2024/5, CHEM08030_VV1_SEM1_2024/5</t>
+          <t>CHEM08019_SV1_YR_2024/5, CHPH08002_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Biological Chemistry 2, Biological Chemistry 2</t>
+          <t>Chemistry 2, Chemistry for Chemical Physics 2, Chemistry 2A</t>
         </is>
       </c>
       <c r="K124" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>10, 12, 14, 16</t>
+          <t>10, 11, 12, 13, 14, 15</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -7893,17 +7887,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>E:HP814ZRIZI</t>
+          <t>E:2ZR529FIMM</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0632_00_G.A04</t>
+          <t>0639_03_3.03</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -7912,12 +7906,12 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Chemistry 3P - Lab (P)/Group D</t>
+          <t>Biological Chemistry 2 - Laboratory/Yellow Group</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -7927,12 +7921,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>CHEM09007_SV1_YR_2024/5</t>
+          <t>CHEM08030_SV1_SEM1_2024/5, CHEM08030_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Chemistry 3P Practical and Transferable Skills</t>
+          <t>Biological Chemistry 2, Biological Chemistry 2</t>
         </is>
       </c>
       <c r="K125" t="n">
@@ -7940,7 +7934,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>10, 11, 12, 13, 14, 15</t>
+          <t>10, 12, 14, 16</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -7952,17 +7946,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>E:WHML9Z9JRE</t>
+          <t>E:5DRWXSYTTF</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0632_01_1.A10</t>
+          <t>0654_-1_LG.01</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -7970,36 +7964,34 @@
           <t>fixed_non_vet</t>
         </is>
       </c>
-      <c r="E126" t="n">
-        <v>22</v>
-      </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Chemistry 3P - Lab (O)/Group A</t>
+          <t>Advanced Topics in Chemical Physics - Machine Learning Workshop</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Laboratory</t>
+          <t>Computer Workshop</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>CHEM09007_SV1_YR_2024/5</t>
+          <t>CHPH11004_SS1_YR_2024/5</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Chemistry 3P Practical and Transferable Skills</t>
+          <t>Advanced Topics in Chemical Physics</t>
         </is>
       </c>
       <c r="K126" t="n">
-        <v>170</v>
+        <v>230</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 14, 15</t>
+          <t>10, 11</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -8011,17 +8003,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>E:EJIU85QYHX</t>
+          <t>E:QEZ55X6R21</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0632_00_G.A04</t>
+          <t>0632_01_1.A04</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -8030,12 +8022,12 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Chemistry 3P - Lab (P)/Group E</t>
+          <t>Chemistry 2 - Inorganic Lab/Tpm</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8045,16 +8037,16 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>CHEM09007_SV1_YR_2024/5</t>
+          <t>CHPH08002_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5, CHEM08019_SV1_YR_2024/5</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Chemistry 3P Practical and Transferable Skills</t>
+          <t>Chemistry for Chemical Physics 2, Chemistry 2A, Chemistry 2</t>
         </is>
       </c>
       <c r="K127" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="L127" t="inlineStr">
         <is>
@@ -8070,7 +8062,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>E:34MPVI6AF1</t>
+          <t>E:CXBMOSH7E5</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8080,7 +8072,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -8094,7 +8086,7 @@
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Chemistry 2 - Inorganic Lab/Fam</t>
+          <t>Chemistry 2 - Inorganic Lab/Wam</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8129,17 +8121,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>E:2ZR529FIMM</t>
+          <t>E:ETCOD19WQ3</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0639_03_3.03</t>
+          <t>0632_01_1.A04</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8148,12 +8140,12 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Biological Chemistry 2 - Laboratory/Yellow Group</t>
+          <t>Chemistry 2 - Inorganic Lab/Mam</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8163,20 +8155,20 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>CHEM08030_SV1_SEM1_2024/5, CHEM08030_VV1_SEM1_2024/5</t>
+          <t>CHEM08019_SV1_YR_2024/5, CHPH08002_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Biological Chemistry 2, Biological Chemistry 2</t>
+          <t>Chemistry 2, Chemistry for Chemical Physics 2, Chemistry 2A</t>
         </is>
       </c>
       <c r="K129" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>10, 12, 14, 16</t>
+          <t>10, 11, 12, 13, 14, 15</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -8188,17 +8180,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>E:5DRWXSYTTF</t>
+          <t>E:O8MLWV2FM4</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0654_-1_LG.01</t>
+          <t>0639_03_3.03</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -8206,34 +8198,36 @@
           <t>fixed_non_vet</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr"/>
+      <c r="E130" t="n">
+        <v>90</v>
+      </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Advanced Topics in Chemical Physics - Machine Learning Workshop</t>
+          <t>Biological Chemistry 1A - Lab Group/2A</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Computer Workshop</t>
+          <t>Laboratory</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>CHPH11004_SS1_YR_2024/5</t>
+          <t>CHEM08022_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Advanced Topics in Chemical Physics</t>
+          <t>Biological Chemistry 1A</t>
         </is>
       </c>
       <c r="K130" t="n">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>10, 11</t>
+          <t>10, 12, 14, 16, 18</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -8245,17 +8239,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>E:QEZ55X6R21</t>
+          <t>E:186LT2Q53I</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0632_01_1.A04</t>
+          <t>0632_01_1.A10</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -8264,12 +8258,12 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Chemistry 2 - Inorganic Lab/Tpm</t>
+          <t>Chemistry 3P - Lab (O)/Group A</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8279,20 +8273,20 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>CHPH08002_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5, CHEM08019_SV1_YR_2024/5</t>
+          <t>CHEM09007_SV1_YR_2024/5</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Chemistry for Chemical Physics 2, Chemistry 2A, Chemistry 2</t>
+          <t>Chemistry 3P Practical and Transferable Skills</t>
         </is>
       </c>
       <c r="K131" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>10, 11, 12, 13, 14, 15</t>
+          <t>9, 10, 11, 12, 13, 14, 15</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -8304,17 +8298,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>E:CXBMOSH7E5</t>
+          <t>E:OJW8RO4669</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0632_01_1.A04</t>
+          <t>0632_01_1.A10</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -8323,12 +8317,12 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Chemistry 2 - Inorganic Lab/Wam</t>
+          <t>Chemistry 3P - Lab (O)/Group A</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8338,12 +8332,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>CHEM08019_SV1_YR_2024/5, CHPH08002_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5</t>
+          <t>CHEM09007_SV1_YR_2024/5</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Chemistry 2, Chemistry for Chemical Physics 2, Chemistry 2A</t>
+          <t>Chemistry 3P Practical and Transferable Skills</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -8351,7 +8345,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>10, 11, 12, 13, 14, 15</t>
+          <t>9, 10, 11, 12, 13, 14, 15</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -8363,17 +8357,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>E:ETCOD19WQ3</t>
+          <t>E:21NDJOLUTR</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0632_01_1.A04</t>
+          <t>0639_03_3.03</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -8382,12 +8376,12 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Chemistry 2 - Inorganic Lab/Mam</t>
+          <t>Biological Chemistry 2 - Laboratory/Indigo Group</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8397,20 +8391,20 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>CHEM08019_SV1_YR_2024/5, CHPH08002_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5</t>
+          <t>CHEM08030_VV1_SEM1_2024/5, CHEM08030_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Chemistry 2, Chemistry for Chemical Physics 2, Chemistry 2A</t>
+          <t>Biological Chemistry 2, Biological Chemistry 2</t>
         </is>
       </c>
       <c r="K133" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>10, 11, 12, 13, 14, 15</t>
+          <t>10, 12, 14, 16</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -8422,12 +8416,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>E:O8MLWV2FM4</t>
+          <t>E:QYCJUUEYK8</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0639_03_3.03</t>
+          <t>0632_00_G.A04</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8441,12 +8435,12 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Biological Chemistry 1A - Lab Group/2A</t>
+          <t>Chemistry 3P - Lab (P)/Group F</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8456,12 +8450,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>CHEM08022_SV1_SEM1_2024/5</t>
+          <t>CHEM09007_SV1_YR_2024/5</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Biological Chemistry 1A</t>
+          <t>Chemistry 3P Practical and Transferable Skills</t>
         </is>
       </c>
       <c r="K134" t="n">
@@ -8469,7 +8463,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>10, 12, 14, 16, 18</t>
+          <t>10, 11, 12, 13, 14, 15</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -8481,17 +8475,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>E:186LT2Q53I</t>
+          <t>E:Q84ZKNQT48</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0632_01_1.A10</t>
+          <t>0639_03_3.03</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -8500,12 +8494,12 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Chemistry 3P - Lab (O)/Group A</t>
+          <t>Biological Chemistry 2 - Laboratory/Green Group</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8515,20 +8509,20 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>CHEM09007_SV1_YR_2024/5</t>
+          <t>CHEM08030_VV1_SEM1_2024/5, CHEM08030_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Chemistry 3P Practical and Transferable Skills</t>
+          <t>Biological Chemistry 2, Biological Chemistry 2</t>
         </is>
       </c>
       <c r="K135" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 14, 15</t>
+          <t>10, 12, 14, 16</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -8540,7 +8534,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>E:OJW8RO4669</t>
+          <t>E:MM3QNBDN5V</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8550,7 +8544,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -8564,7 +8558,7 @@
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Chemistry 3P - Lab (O)/Group A</t>
+          <t>Chemistry 3P - Lab (O)/Group C</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8583,7 +8577,7 @@
         </is>
       </c>
       <c r="K136" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -8599,17 +8593,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>E:21NDJOLUTR</t>
+          <t>E:FCH7IGJ31N</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0639_03_3.03</t>
+          <t>0632_01_1.A10</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8618,12 +8612,12 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Biological Chemistry 2 - Laboratory/Indigo Group</t>
+          <t>Chemistry 3P - Lab (O)/Group C</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8633,20 +8627,20 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>CHEM08030_VV1_SEM1_2024/5, CHEM08030_SV1_SEM1_2024/5</t>
+          <t>CHEM09007_SV1_YR_2024/5</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Biological Chemistry 2, Biological Chemistry 2</t>
+          <t>Chemistry 3P Practical and Transferable Skills</t>
         </is>
       </c>
       <c r="K137" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>10, 12, 14, 16</t>
+          <t>9, 10, 11, 12, 13, 14, 15</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -8658,17 +8652,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>E:QYCJUUEYK8</t>
+          <t>E:EGL9OL3C8K</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0632_00_G.A04</t>
+          <t>0632_01_1.A04</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8677,12 +8671,12 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Chemistry 3P - Lab (P)/Group F</t>
+          <t>Chemistry 2 - Inorganic Lab/Mam</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8692,12 +8686,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>CHEM09007_SV1_YR_2024/5</t>
+          <t>CHPH08002_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5, CHEM08019_SV1_YR_2024/5</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Chemistry 3P Practical and Transferable Skills</t>
+          <t>Chemistry for Chemical Physics 2, Chemistry 2A, Chemistry 2</t>
         </is>
       </c>
       <c r="K138" t="n">
@@ -8717,7 +8711,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>E:Q84ZKNQT48</t>
+          <t>E:TWBJKUG5XC</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8727,7 +8721,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -8736,12 +8730,12 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Biological Chemistry 2 - Laboratory/Green Group</t>
+          <t>Biological Chemistry 1A - Lab Group/1A</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8751,20 +8745,20 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>CHEM08030_VV1_SEM1_2024/5, CHEM08030_SV1_SEM1_2024/5</t>
+          <t>CHEM08022_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Biological Chemistry 2, Biological Chemistry 2</t>
+          <t>Biological Chemistry 1A</t>
         </is>
       </c>
       <c r="K139" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>10, 12, 14, 16</t>
+          <t>10, 12, 14, 16, 18</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -8776,17 +8770,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>E:MM3QNBDN5V</t>
+          <t>E:VVSDB35D7I</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0632_01_1.A10</t>
+          <t>0632_01_1.A04</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8795,12 +8789,12 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Chemistry 3P - Lab (O)/Group C</t>
+          <t>Chemistry 2 - Inorganic Lab/Thpm</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8810,12 +8804,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>CHEM09007_SV1_YR_2024/5</t>
+          <t>CHEM08019_SV1_YR_2024/5, CHPH08002_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Chemistry 3P Practical and Transferable Skills</t>
+          <t>Chemistry 2, Chemistry for Chemical Physics 2, Chemistry 2A</t>
         </is>
       </c>
       <c r="K140" t="n">
@@ -8823,7 +8817,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 14, 15</t>
+          <t>10, 11, 12, 13, 14, 15</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -8835,17 +8829,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>E:FCH7IGJ31N</t>
+          <t>E:YOUCJRFRW1</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0632_01_1.A10</t>
+          <t>0632_01_1.A04</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -8854,12 +8848,12 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Chemistry 3P - Lab (O)/Group C</t>
+          <t>Chemistry 2 - Inorganic Lab/Tpm</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -8869,20 +8863,20 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>CHEM09007_SV1_YR_2024/5</t>
+          <t>CHEM08026_VV1_SEM1_2024/5, CHEM08019_SV1_YR_2024/5, CHPH08002_SV1_YR_2024/5</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Chemistry 3P Practical and Transferable Skills</t>
+          <t>Chemistry 2A, Chemistry 2, Chemistry for Chemical Physics 2</t>
         </is>
       </c>
       <c r="K141" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 14, 15</t>
+          <t>10, 11, 12, 13, 14, 15</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -8894,17 +8888,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>E:EGL9OL3C8K</t>
+          <t>E:N25MR4P2SD</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0632_01_1.A04</t>
+          <t>0639_03_3.03</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -8913,12 +8907,12 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Chemistry 2 - Inorganic Lab/Mam</t>
+          <t>Biological Chemistry 2 - Laboratory/Violet Group</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -8928,20 +8922,20 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>CHPH08002_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5, CHEM08019_SV1_YR_2024/5</t>
+          <t>CHEM08030_SV1_SEM1_2024/5, CHEM08030_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Chemistry for Chemical Physics 2, Chemistry 2A, Chemistry 2</t>
+          <t>Biological Chemistry 2, Biological Chemistry 2</t>
         </is>
       </c>
       <c r="K142" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>10, 11, 12, 13, 14, 15</t>
+          <t>10, 12, 14, 16</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -8953,17 +8947,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>E:TWBJKUG5XC</t>
+          <t>E:UL8H9KDI8I</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0639_03_3.03</t>
+          <t>0632_01_1.A10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -8972,12 +8966,12 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Biological Chemistry 1A - Lab Group/1A</t>
+          <t>Chemistry 3P - Lab (O)/Group B</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -8987,20 +8981,20 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>CHEM08022_SV1_SEM1_2024/5</t>
+          <t>CHEM09007_SV1_YR_2024/5</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Biological Chemistry 1A</t>
+          <t>Chemistry 3P Practical and Transferable Skills</t>
         </is>
       </c>
       <c r="K143" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>10, 12, 14, 16, 18</t>
+          <t>9, 10, 11, 12, 13, 14, 15</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -9012,7 +9006,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>E:VVSDB35D7I</t>
+          <t>E:UXYD57AI9S</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9022,7 +9016,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -9036,7 +9030,7 @@
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Chemistry 2 - Inorganic Lab/Thpm</t>
+          <t>Chemistry 2 - Inorganic Lab Fpm</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9071,17 +9065,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>E:YOUCJRFRW1</t>
+          <t>E:EEPMR75NO2</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0632_01_1.A04</t>
+          <t>0632_01_1.A10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -9090,12 +9084,12 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Chemistry 2 - Inorganic Lab/Tpm</t>
+          <t>Chemistry 3P - Lab (O)/Group B</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9105,20 +9099,20 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>CHEM08026_VV1_SEM1_2024/5, CHEM08019_SV1_YR_2024/5, CHPH08002_SV1_YR_2024/5</t>
+          <t>CHEM09007_SV1_YR_2024/5</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Chemistry 2A, Chemistry 2, Chemistry for Chemical Physics 2</t>
+          <t>Chemistry 3P Practical and Transferable Skills</t>
         </is>
       </c>
       <c r="K145" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>10, 11, 12, 13, 14, 15</t>
+          <t>9, 10, 11, 12, 13, 14, 15</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -9130,17 +9124,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>E:N25MR4P2SD</t>
+          <t>E:8NEGGICPOU</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0639_03_3.03</t>
+          <t>0632_01_1.A10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9149,12 +9143,12 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Biological Chemistry 2 - Laboratory/Violet Group</t>
+          <t>Chemistry 3P - Lab (O)/Group B</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9164,12 +9158,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>CHEM08030_SV1_SEM1_2024/5, CHEM08030_VV1_SEM1_2024/5</t>
+          <t>CHEM09007_SV1_YR_2024/5</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Biological Chemistry 2, Biological Chemistry 2</t>
+          <t>Chemistry 3P Practical and Transferable Skills</t>
         </is>
       </c>
       <c r="K146" t="n">
@@ -9177,7 +9171,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>10, 12, 14, 16</t>
+          <t>9, 10, 11, 12, 13, 14, 15</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -9189,17 +9183,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>E:UL8H9KDI8I</t>
+          <t>E:4YUBD63UYE</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0632_01_1.A10</t>
+          <t>0632_01_1.A04</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9208,12 +9202,12 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Chemistry 3P - Lab (O)/Group B</t>
+          <t>Chemistry 2 - Inorganic Lab/Tam</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9223,20 +9217,20 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>CHEM09007_SV1_YR_2024/5</t>
+          <t>CHEM08019_SV1_YR_2024/5, CHPH08002_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Chemistry 3P Practical and Transferable Skills</t>
+          <t>Chemistry 2, Chemistry for Chemical Physics 2, Chemistry 2A</t>
         </is>
       </c>
       <c r="K147" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 14, 15</t>
+          <t>10, 11, 12, 13, 14, 15</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -9248,7 +9242,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>E:UXYD57AI9S</t>
+          <t>E:LP62JAHNA8</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9258,7 +9252,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9267,12 +9261,12 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Chemistry 2 - Inorganic Lab Fpm</t>
+          <t>Chemistry 2 - Inorganic Lab/Thpm</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9307,17 +9301,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>E:EEPMR75NO2</t>
+          <t>E:8XQV144SN4</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0632_01_1.A10</t>
+          <t>0639_03_3.03</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -9326,12 +9320,12 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Chemistry 3P - Lab (O)/Group B</t>
+          <t>Biological Chemistry 1A - Lab Group/3A</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9341,12 +9335,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>CHEM09007_SV1_YR_2024/5</t>
+          <t>CHEM08022_SV1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Chemistry 3P Practical and Transferable Skills</t>
+          <t>Biological Chemistry 1A</t>
         </is>
       </c>
       <c r="K149" t="n">
@@ -9354,7 +9348,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 14, 15</t>
+          <t>10, 12, 14, 16, 18</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -9366,17 +9360,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>E:8NEGGICPOU</t>
+          <t>E:8QXX3J178S</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0632_01_1.A10</t>
+          <t>0632_00_G.A07</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -9385,12 +9379,12 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Chemistry 3P - Lab (O)/Group B</t>
+          <t>Laboratory Techniques 1 Chemistry PGT - Laboratory/Materials Group</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9400,12 +9394,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>CHEM09007_SV1_YR_2024/5</t>
+          <t>CHEM11082_SS1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Chemistry 3P Practical and Transferable Skills</t>
+          <t>Laboratory Techniques 1 Chemistry PGT</t>
         </is>
       </c>
       <c r="K150" t="n">
@@ -9413,7 +9407,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>9, 10, 11, 12, 13, 14, 15</t>
+          <t>9, 10, 11, 13, 14, 15, 16, 17, 18</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -9425,17 +9419,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>E:4YUBD63UYE</t>
+          <t>E:MTXIIZMSF2</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0632_01_1.A04</t>
+          <t>0632_01_1.A10</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9444,12 +9438,12 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Chemistry 2 - Inorganic Lab/Tam</t>
+          <t>Chemistry 3P - Lab (O)/Group C</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9459,20 +9453,20 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>CHEM08019_SV1_YR_2024/5, CHPH08002_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5</t>
+          <t>CHEM09007_SV1_YR_2024/5</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Chemistry 2, Chemistry for Chemical Physics 2, Chemistry 2A</t>
+          <t>Chemistry 3P Practical and Transferable Skills</t>
         </is>
       </c>
       <c r="K151" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>10, 11, 12, 13, 14, 15</t>
+          <t>9, 10, 11, 12, 13, 14, 15</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -9484,17 +9478,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>E:LP62JAHNA8</t>
+          <t>E:2AKQ76N7X1</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0632_01_1.A04</t>
+          <t>0632_01_1.A10</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -9503,12 +9497,12 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Chemistry 2 - Inorganic Lab/Thpm</t>
+          <t>Chemistry 3P - Lab (O)/Group B</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9518,20 +9512,20 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>CHEM08019_SV1_YR_2024/5, CHPH08002_SV1_YR_2024/5, CHEM08026_VV1_SEM1_2024/5</t>
+          <t>CHEM09007_SV1_YR_2024/5</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Chemistry 2, Chemistry for Chemical Physics 2, Chemistry 2A</t>
+          <t>Chemistry 3P Practical and Transferable Skills</t>
         </is>
       </c>
       <c r="K152" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>10, 11, 12, 13, 14, 15</t>
+          <t>9, 10, 11, 12, 13, 14, 15</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -9543,17 +9537,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>E:8XQV144SN4</t>
+          <t>E:9FAUS5M3BO</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0639_03_3.03</t>
+          <t>0632_00_G.A07</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -9562,12 +9556,12 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Biological Chemistry 1A - Lab Group/3A</t>
+          <t>Laboratory Techniques 1 Chemistry PGT - Laboratory/Analytical Group</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9577,259 +9571,23 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>CHEM08022_SV1_SEM1_2024/5</t>
+          <t>CHEM11082_SS1_SEM1_2024/5</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Biological Chemistry 1A</t>
+          <t>Laboratory Techniques 1 Chemistry PGT</t>
         </is>
       </c>
       <c r="K153" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>10, 12, 14, 16, 18</t>
+          <t>9, 10, 11, 13, 14, 15, 16, 17, 18</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
-        <is>
-          <t>Semester 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>E:8QXX3J178S</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>0632_00_G.A07</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Tuesday 14:00</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>fixed_non_vet</t>
-        </is>
-      </c>
-      <c r="E154" t="n">
-        <v>25</v>
-      </c>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>Laboratory Techniques 1 Chemistry PGT - Laboratory/Materials Group</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Laboratory</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>CHEM11082_SS1_SEM1_2024/5</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>Laboratory Techniques 1 Chemistry PGT</t>
-        </is>
-      </c>
-      <c r="K154" t="n">
-        <v>170</v>
-      </c>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>9, 10, 11, 13, 14, 15, 16, 17, 18</t>
-        </is>
-      </c>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>Semester 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>E:MTXIIZMSF2</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>0632_01_1.A10</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Thursday 14:00</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>fixed_non_vet</t>
-        </is>
-      </c>
-      <c r="E155" t="n">
-        <v>22</v>
-      </c>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>Chemistry 3P - Lab (O)/Group C</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Laboratory</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>CHEM09007_SV1_YR_2024/5</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>Chemistry 3P Practical and Transferable Skills</t>
-        </is>
-      </c>
-      <c r="K155" t="n">
-        <v>170</v>
-      </c>
-      <c r="L155" t="inlineStr">
-        <is>
-          <t>9, 10, 11, 12, 13, 14, 15</t>
-        </is>
-      </c>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>Semester 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>E:2AKQ76N7X1</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>0632_01_1.A10</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Friday 09:00</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>fixed_non_vet</t>
-        </is>
-      </c>
-      <c r="E156" t="n">
-        <v>22</v>
-      </c>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>Chemistry 3P - Lab (O)/Group B</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Laboratory</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>CHEM09007_SV1_YR_2024/5</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>Chemistry 3P Practical and Transferable Skills</t>
-        </is>
-      </c>
-      <c r="K156" t="n">
-        <v>180</v>
-      </c>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>9, 10, 11, 12, 13, 14, 15</t>
-        </is>
-      </c>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>Semester 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>E:9FAUS5M3BO</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>0632_00_G.A07</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Monday 14:00</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>fixed_non_vet</t>
-        </is>
-      </c>
-      <c r="E157" t="n">
-        <v>25</v>
-      </c>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>Laboratory Techniques 1 Chemistry PGT - Laboratory/Analytical Group</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Laboratory</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>CHEM11082_SS1_SEM1_2024/5</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>Laboratory Techniques 1 Chemistry PGT</t>
-        </is>
-      </c>
-      <c r="K157" t="n">
-        <v>170</v>
-      </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>9, 10, 11, 13, 14, 15, 16, 17, 18</t>
-        </is>
-      </c>
-      <c r="M157" t="inlineStr">
         <is>
           <t>Semester 1</t>
         </is>
